--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17249</v>
+        <v>16221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0164</v>
+        <v>0.0155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81076</v>
+        <v>76062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38376</v>
+        <v>35976</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0343</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19376</v>
+        <v>18718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173580</v>
+        <v>163522</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1655</v>
+        <v>0.1559</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>469462</v>
+        <v>442507</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4477</v>
+        <v>0.422</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16845</v>
+        <v>14980</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0161</v>
+        <v>0.0143</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55994</v>
+        <v>53125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0534</v>
+        <v>0.0507</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2142</v>
+        <v>2016</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8656</v>
+        <v>8164</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5301</v>
+        <v>5251</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6375</v>
+        <v>6314</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34106</v>
+        <v>33067</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0325</v>
+        <v>0.0315</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161657</v>
+        <v>155672</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1485</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71392</v>
+        <v>68864</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33096</v>
+        <v>32390</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.0309</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4716</v>
+        <v>4563</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18444</v>
+        <v>17859</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6857</v>
+        <v>6774</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7790</v>
+        <v>7728</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-09 12:19:12</t>
+          <t>2026-07-09 13:34:29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.csv</t>
+          <t>lista_arquivos_disponiveis.csv</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
+          <t>data/final/documentacao/lista_arquivos_disponiveis.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1399,97 +1399,97 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17080</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0163</v>
+        <v>0.0061</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:42</t>
+          <t>2026-07-09 13:33:20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.json</t>
+          <t>lista_arquivos_disponiveis.xlsx</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
+          <t>data/final/documentacao/lista_arquivos_disponiveis.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>56061</v>
+        <v>6993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0535</v>
+        <v>0.0067</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:42</t>
+          <t>2026-07-09 13:33:20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.parquet</t>
+          <t>lista_series_individuais.csv</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
+          <t>data/final/documentacao/lista_series_individuais.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31025</v>
+        <v>10127</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0296</v>
+        <v>0.0097</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:42</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.xlsx</t>
+          <t>lista_series_individuais.xlsx</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
+          <t>data/final/documentacao/lista_series_individuais.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,64 +1498,64 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>19027</v>
+        <v>7968</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0181</v>
+        <v>0.0076</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:42</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.csv</t>
+          <t>resumo_site.json</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
+          <t>data/final/documentacao/resumo_site.json</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>133373</v>
+        <v>672</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1272</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:42</t>
+          <t>2026-07-09 13:33:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.json</t>
+          <t>ultima_atualizacao.json</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
+          <t>data/final/documentacao/ultima_atualizacao.json</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,64 +1564,64 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>427185</v>
+        <v>289</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4074</v>
+        <v>0.0003</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:33:20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.parquet</t>
+          <t>bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>23538</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0224</v>
+        <v>0.0011</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.xlsx</t>
+          <t>bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60805</v>
+        <v>5879</v>
       </c>
       <c r="F37" t="n">
-        <v>0.058</v>
+        <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.csv</t>
+          <t>bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1663,97 +1663,97 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5292</v>
+        <v>1226</v>
       </c>
       <c r="F38" t="n">
-        <v>0.005</v>
+        <v>0.0012</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.json</t>
+          <t>bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>15205</v>
+        <v>5818</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0145</v>
+        <v>0.0055</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.parquet</t>
+          <t>bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>9745</v>
+        <v>1135</v>
       </c>
       <c r="F40" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.xlsx</t>
+          <t>bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1762,31 +1762,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7127</v>
+        <v>5812</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0068</v>
+        <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1795,113 +1795,4403 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>822</v>
+        <v>954</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.json</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3310</v>
+        <v>5725</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0032</v>
+        <v>0.0055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.parquet</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4571</v>
+        <v>954</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0044</v>
+        <v>0.0009</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-09 12:18:43</t>
+          <t>2026-07-09 13:34:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5736</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_total.csv</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>958</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5731</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>958</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5764</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>930</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta.xlsx</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5812</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ibc_br.csv</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ibc_br.xlsx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5933</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ibc_br_sa.csv</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1215</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ibc_br_sa.xlsx</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5903</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m.csv</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>991</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m.xlsx</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5804</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5809</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pf.csv</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>955</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5761</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pj.csv</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>952</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5748</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_total.csv</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>954</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5751</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inpc.csv</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>958</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inpc.xlsx</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5774</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inpc_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>974</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inpc_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5757</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ipca.csv</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>963</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ipca.xlsx</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5764</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ipca_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>970</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ipca_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5758</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5799</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5883</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_pf.csv</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5910</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_pj.csv</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5895</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5917</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5690</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1226</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5818</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5985</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br.csv</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1184</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br.xlsx</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5944</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br_sa.csv</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1164</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5894</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1217</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5956</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5918</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5940</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1173</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5917</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>yahoo_bova11.csv</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_bova11.csv</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1307</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>yahoo_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5937</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>yahoo_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1107</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>yahoo_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>5866</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>yahoo_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1464</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>yahoo_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6068</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>yahoo_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1142</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>yahoo_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>5881</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>yahoo_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>yahoo_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5902</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>yahoo_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1271</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>yahoo_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5918</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>yahoo_milho.csv</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_milho.csv</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>yahoo_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>5827</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>yahoo_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1471</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>yahoo_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6077</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>yahoo_ouro.csv</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ouro.csv</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>yahoo_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5917</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5957</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5937</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>yahoo_ret_bova11.csv</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>yahoo_ret_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5994</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5995</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5995</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>yahoo_ret_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>yahoo_ret_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>5976</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6007</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5995</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>yahoo_ret_milho.csv</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>yahoo_ret_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6015</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>yahoo_ret_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>yahoo_ret_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6014</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ouro.csv</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6009</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1252</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6027</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6019</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>yahoo_ret_smal11.csv</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1251</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>yahoo_ret_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6014</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>yahoo_ret_soja.csv</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>yahoo_ret_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6018</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>yahoo_ret_sp500.csv</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1232</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>yahoo_ret_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6003</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>yahoo_smal11.csv</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_smal11.csv</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>yahoo_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>5918</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>yahoo_soja.csv</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_soja.csv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1139</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>yahoo_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>5835</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>yahoo_sp500.csv</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_sp500.csv</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>yahoo_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6029</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.csv</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>17085</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.json</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>56066</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.parquet</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>31025</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.xlsx</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>19037</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.csv</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>133378</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.json</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>427190</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.parquet</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>23549</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.xlsx</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>60817</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>5292</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.json</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>9745</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>7127</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>826</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>3314</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>4572</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>data/final/yahoo/resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>data/final/yahoo</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>.xlsx</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>5565</v>
-      </c>
-      <c r="F45" t="n">
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>5571</v>
+      </c>
+      <c r="F175" t="n">
         <v>0.0053</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-07-09 12:18:43</t>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:33:38</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16221</v>
+        <v>17249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0155</v>
+        <v>0.0164</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76062</v>
+        <v>81076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0725</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35976</v>
+        <v>38376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0343</v>
+        <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18718</v>
+        <v>19377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0179</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>163522</v>
+        <v>173580</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1559</v>
+        <v>0.1655</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>442507</v>
+        <v>469462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.422</v>
+        <v>0.4477</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14980</v>
+        <v>15260</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0143</v>
+        <v>0.0146</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53125</v>
+        <v>55991</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0507</v>
+        <v>0.0534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2016</v>
+        <v>2142</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8164</v>
+        <v>8656</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5251</v>
+        <v>5301</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6314</v>
+        <v>6378</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33067</v>
+        <v>34107</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0315</v>
+        <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>155672</v>
+        <v>161658</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1485</v>
+        <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68864</v>
+        <v>71392</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32390</v>
+        <v>33099</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0309</v>
+        <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4563</v>
+        <v>4717</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17859</v>
+        <v>18445</v>
       </c>
       <c r="F23" t="n">
-        <v>0.017</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6774</v>
+        <v>6839</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7728</v>
+        <v>7791</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:27</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>22691</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0061</v>
+        <v>0.0216</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:20</t>
+          <t>2026-07-10 12:26:32</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6993</v>
+        <v>12084</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0067</v>
+        <v>0.0115</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:20</t>
+          <t>2026-07-10 12:26:32</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10127</v>
+        <v>10491</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7968</v>
+        <v>8056</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:20</t>
+          <t>2026-07-10 12:26:32</t>
         </is>
       </c>
     </row>
@@ -1571,19 +1571,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:20</t>
+          <t>2026-07-10 12:26:32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd.csv</t>
+          <t>bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1597,26 +1597,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="F36" t="n">
         <v>0.0011</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1630,26 +1630,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5879</v>
+        <v>5873</v>
       </c>
       <c r="F37" t="n">
         <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi.csv</t>
+          <t>bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1663,26 +1663,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1226</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi.xlsx</t>
+          <t>bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1696,26 +1696,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5818</v>
+        <v>5879</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi.csv</t>
+          <t>bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1729,26 +1729,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1135</v>
+        <v>1226</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi.xlsx</t>
+          <t>bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1762,26 +1762,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5812</v>
+        <v>5818</v>
       </c>
       <c r="F41" t="n">
         <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1795,26 +1795,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>954</v>
+        <v>1135</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1828,26 +1828,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5725</v>
+        <v>5812</v>
       </c>
       <c r="F43" t="n">
         <v>0.0055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1868,19 +1868,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1894,26 +1894,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5736</v>
+        <v>5725</v>
       </c>
       <c r="F45" t="n">
         <v>0.0055</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1927,26 +1927,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="F46" t="n">
         <v>0.0009</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1960,26 +1960,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5731</v>
+        <v>5736</v>
       </c>
       <c r="F47" t="n">
         <v>0.0055</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2000,19 +2000,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2026,26 +2026,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5764</v>
+        <v>5731</v>
       </c>
       <c r="F49" t="n">
         <v>0.0055</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta.csv</t>
+          <t>bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2059,26 +2059,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="F50" t="n">
         <v>0.0009</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2092,26 +2092,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5660</v>
+        <v>5764</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0054</v>
+        <v>0.0055</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over.csv</t>
+          <t>bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2125,26 +2125,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1135</v>
+        <v>930</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over.xlsx</t>
+          <t>bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2158,26 +2158,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5812</v>
+        <v>5660</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0055</v>
+        <v>0.0054</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br.csv</t>
+          <t>bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2191,26 +2191,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1135</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br.xlsx</t>
+          <t>bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2224,26 +2224,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5933</v>
+        <v>5812</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa.csv</t>
+          <t>bcb_sgs_ibc_br.csv</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2257,26 +2257,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="n">
         <v>0.0012</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>bcb_sgs_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2290,26 +2290,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5903</v>
+        <v>5933</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m.csv</t>
+          <t>bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2323,26 +2323,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>991</v>
+        <v>1215</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m.xlsx</t>
+          <t>bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2356,26 +2356,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5804</v>
+        <v>5903</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2389,26 +2389,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1008</v>
+        <v>991</v>
       </c>
       <c r="F60" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2422,26 +2422,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5809</v>
+        <v>5804</v>
       </c>
       <c r="F61" t="n">
         <v>0.0055</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf.csv</t>
+          <t>bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2455,26 +2455,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>955</v>
+        <v>1008</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2488,26 +2488,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5761</v>
+        <v>5809</v>
       </c>
       <c r="F63" t="n">
         <v>0.0055</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj.csv</t>
+          <t>bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2521,26 +2521,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="F64" t="n">
         <v>0.0009</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2554,26 +2554,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5748</v>
+        <v>5761</v>
       </c>
       <c r="F65" t="n">
         <v>0.0055</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total.csv</t>
+          <t>bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2587,26 +2587,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F66" t="n">
         <v>0.0009</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2620,26 +2620,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5751</v>
+        <v>5748</v>
       </c>
       <c r="F67" t="n">
         <v>0.0055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc.csv</t>
+          <t>bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2653,26 +2653,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="F68" t="n">
         <v>0.0009</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc.xlsx</t>
+          <t>bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2686,26 +2686,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5774</v>
+        <v>5751</v>
       </c>
       <c r="F69" t="n">
         <v>0.0055</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m.csv</t>
+          <t>bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2719,26 +2719,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="F70" t="n">
         <v>0.0009</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2752,26 +2752,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5757</v>
+        <v>5774</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca.csv</t>
+          <t>bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2785,26 +2785,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="F72" t="n">
         <v>0.0009</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca.xlsx</t>
+          <t>bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2818,26 +2818,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5764</v>
+        <v>5757</v>
       </c>
       <c r="F73" t="n">
         <v>0.0055</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m.csv</t>
+          <t>bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2851,26 +2851,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="F74" t="n">
         <v>0.0009</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2884,26 +2884,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total.csv</t>
+          <t>bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1012</v>
+        <v>970</v>
       </c>
       <c r="F76" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total.xlsx</t>
+          <t>bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2950,26 +2950,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5799</v>
+        <v>5758</v>
       </c>
       <c r="F77" t="n">
         <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais.csv</t>
+          <t>bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1214</v>
+        <v>1012</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3016,26 +3016,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5883</v>
+        <v>5799</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf.csv</t>
+          <t>bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3049,26 +3049,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1253</v>
+        <v>1214</v>
       </c>
       <c r="F80" t="n">
         <v>0.0012</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3082,26 +3082,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5910</v>
+        <v>5883</v>
       </c>
       <c r="F81" t="n">
         <v>0.0056</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj.csv</t>
+          <t>bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3148,26 +3148,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5895</v>
+        <v>5910</v>
       </c>
       <c r="F83" t="n">
         <v>0.0056</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total.csv</t>
+          <t>bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3188,19 +3188,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3214,26 +3214,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5917</v>
+        <v>5895</v>
       </c>
       <c r="F85" t="n">
         <v>0.0056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta.csv</t>
+          <t>bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3247,26 +3247,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1029</v>
+        <v>1253</v>
       </c>
       <c r="F86" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta.xlsx</t>
+          <t>bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3280,26 +3280,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5690</v>
+        <v>5917</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0054</v>
+        <v>0.0056</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over.csv</t>
+          <t>bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3313,26 +3313,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1226</v>
+        <v>1029</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over.xlsx</t>
+          <t>bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5818</v>
+        <v>5690</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0055</v>
+        <v>0.0054</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3379,26 +3379,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1237</v>
+        <v>1226</v>
       </c>
       <c r="F90" t="n">
         <v>0.0012</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5985</v>
+        <v>5818</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3445,26 +3445,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1184</v>
+        <v>1237</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3478,26 +3478,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5944</v>
+        <v>5979</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3511,26 +3511,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1164</v>
+        <v>1237</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3544,26 +3544,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5894</v>
+        <v>5985</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais.csv</t>
+          <t>bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3577,26 +3577,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1217</v>
+        <v>1184</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+          <t>bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3610,26 +3610,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5956</v>
+        <v>5944</v>
       </c>
       <c r="F97" t="n">
         <v>0.0057</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3643,26 +3643,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="F98" t="n">
         <v>0.0011</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3676,26 +3676,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5918</v>
+        <v>5894</v>
       </c>
       <c r="F99" t="n">
         <v>0.0056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1185</v>
+        <v>1217</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3742,26 +3742,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5940</v>
+        <v>5956</v>
       </c>
       <c r="F101" t="n">
         <v>0.0057</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3775,26 +3775,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3808,26 +3808,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>yahoo_bova11.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3841,26 +3841,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1307</v>
+        <v>1185</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>yahoo_bova11.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3874,26 +3874,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5937</v>
+        <v>5940</v>
       </c>
       <c r="F105" t="n">
         <v>0.0057</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3907,26 +3907,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1107</v>
+        <v>1173</v>
       </c>
       <c r="F106" t="n">
         <v>0.0011</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3940,26 +3940,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5866</v>
+        <v>5917</v>
       </c>
       <c r="F107" t="n">
         <v>0.0056</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones.csv</t>
+          <t>yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3973,26 +3973,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1464</v>
+        <v>1307</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones.xlsx</t>
+          <t>yahoo_bova11.xlsx</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4006,26 +4006,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6068</v>
+        <v>5935</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>yahoo_euro_real.csv</t>
+          <t>yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4039,26 +4039,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1142</v>
+        <v>1107</v>
       </c>
       <c r="F110" t="n">
         <v>0.0011</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>yahoo_euro_real.xlsx</t>
+          <t>yahoo_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5881</v>
+        <v>5866</v>
       </c>
       <c r="F111" t="n">
         <v>0.0056</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa.csv</t>
+          <t>yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4105,26 +4105,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1237</v>
+        <v>1464</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa.xlsx</t>
+          <t>yahoo_dow_jones.xlsx</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4138,26 +4138,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5902</v>
+        <v>6068</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0056</v>
+        <v>0.0058</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11.csv</t>
+          <t>yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4171,26 +4171,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1271</v>
+        <v>1142</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11.xlsx</t>
+          <t>yahoo_euro_real.xlsx</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4204,26 +4204,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5918</v>
+        <v>5879</v>
       </c>
       <c r="F115" t="n">
         <v>0.0056</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>yahoo_milho.csv</t>
+          <t>yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4237,26 +4237,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1080</v>
+        <v>1233</v>
       </c>
       <c r="F116" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>yahoo_milho.xlsx</t>
+          <t>yahoo_ibovespa.xlsx</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4270,26 +4270,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5827</v>
+        <v>5895</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq.csv</t>
+          <t>yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4303,26 +4303,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1471</v>
+        <v>1271</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq.xlsx</t>
+          <t>yahoo_ivvb11.xlsx</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4336,26 +4336,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6077</v>
+        <v>5915</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0058</v>
+        <v>0.0056</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>yahoo_ouro.csv</t>
+          <t>yahoo_milho.csv</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4369,26 +4369,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1347</v>
+        <v>1081</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0013</v>
+        <v>0.001</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>yahoo_ouro.xlsx</t>
+          <t>yahoo_milho.xlsx</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4402,26 +4402,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5917</v>
+        <v>5828</v>
       </c>
       <c r="F121" t="n">
         <v>0.0056</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent.csv</t>
+          <t>yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4435,26 +4435,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1287</v>
+        <v>1471</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent.xlsx</t>
+          <t>yahoo_nasdaq.xlsx</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4468,26 +4468,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5957</v>
+        <v>6077</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti.csv</t>
+          <t>yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4501,26 +4501,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1266</v>
+        <v>1347</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti.xlsx</t>
+          <t>yahoo_ouro.xlsx</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4534,26 +4534,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5937</v>
+        <v>5918</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11.csv</t>
+          <t>yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4567,26 +4567,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1243</v>
+        <v>1287</v>
       </c>
       <c r="F126" t="n">
         <v>0.0012</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11.xlsx</t>
+          <t>yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4600,26 +4600,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5994</v>
+        <v>5957</v>
       </c>
       <c r="F127" t="n">
         <v>0.0057</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real.csv</t>
+          <t>yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4633,26 +4633,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1240</v>
+        <v>1266</v>
       </c>
       <c r="F128" t="n">
         <v>0.0012</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real.xlsx</t>
+          <t>yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4666,26 +4666,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5995</v>
+        <v>5937</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones.csv</t>
+          <t>yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4699,26 +4699,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="F130" t="n">
         <v>0.0012</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones.xlsx</t>
+          <t>yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4739,19 +4739,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real.csv</t>
+          <t>yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4765,26 +4765,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F132" t="n">
         <v>0.0012</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real.xlsx</t>
+          <t>yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4798,26 +4798,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5976</v>
+        <v>5995</v>
       </c>
       <c r="F133" t="n">
         <v>0.0057</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa.csv</t>
+          <t>yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4831,26 +4831,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F134" t="n">
         <v>0.0012</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa.xlsx</t>
+          <t>yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4864,26 +4864,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6007</v>
+        <v>5994</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11.csv</t>
+          <t>yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4897,26 +4897,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1230</v>
+        <v>1239</v>
       </c>
       <c r="F136" t="n">
         <v>0.0012</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11.xlsx</t>
+          <t>yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4930,26 +4930,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5995</v>
+        <v>5976</v>
       </c>
       <c r="F137" t="n">
         <v>0.0057</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho.csv</t>
+          <t>yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4963,26 +4963,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="F138" t="n">
         <v>0.0012</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho.xlsx</t>
+          <t>yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4996,26 +4996,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6015</v>
+        <v>6007</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq.csv</t>
+          <t>yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5029,26 +5029,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="F140" t="n">
         <v>0.0012</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq.xlsx</t>
+          <t>yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5062,26 +5062,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6014</v>
+        <v>5995</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro.csv</t>
+          <t>yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5095,26 +5095,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="F142" t="n">
         <v>0.0012</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro.xlsx</t>
+          <t>yahoo_ret_milho.xlsx</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5128,26 +5128,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6009</v>
+        <v>6014</v>
       </c>
       <c r="F143" t="n">
         <v>0.0057</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent.csv</t>
+          <t>yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5161,26 +5161,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1252</v>
+        <v>1238</v>
       </c>
       <c r="F144" t="n">
         <v>0.0012</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent.xlsx</t>
+          <t>yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5194,26 +5194,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6027</v>
+        <v>6014</v>
       </c>
       <c r="F145" t="n">
         <v>0.0057</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti.csv</t>
+          <t>yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5227,26 +5227,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1249</v>
+        <v>1239</v>
       </c>
       <c r="F146" t="n">
         <v>0.0012</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti.xlsx</t>
+          <t>yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5260,26 +5260,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6019</v>
+        <v>6011</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11.csv</t>
+          <t>yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5293,26 +5293,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F148" t="n">
         <v>0.0012</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11.xlsx</t>
+          <t>yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5326,26 +5326,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6014</v>
+        <v>6028</v>
       </c>
       <c r="F149" t="n">
         <v>0.0057</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja.csv</t>
+          <t>yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5359,26 +5359,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1237</v>
+        <v>1249</v>
       </c>
       <c r="F150" t="n">
         <v>0.0012</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja.xlsx</t>
+          <t>yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5392,26 +5392,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="F151" t="n">
         <v>0.0057</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500.csv</t>
+          <t>yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5425,26 +5425,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1232</v>
+        <v>1251</v>
       </c>
       <c r="F152" t="n">
         <v>0.0012</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500.xlsx</t>
+          <t>yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5458,26 +5458,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6003</v>
+        <v>6015</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>yahoo_smal11.csv</t>
+          <t>yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5491,26 +5491,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1266</v>
+        <v>1237</v>
       </c>
       <c r="F154" t="n">
         <v>0.0012</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>yahoo_smal11.xlsx</t>
+          <t>yahoo_ret_soja.xlsx</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5524,26 +5524,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5918</v>
+        <v>6018</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>yahoo_soja.csv</t>
+          <t>yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5557,26 +5557,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1139</v>
+        <v>1231</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>yahoo_soja.xlsx</t>
+          <t>yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5590,26 +5590,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5835</v>
+        <v>6003</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:30</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>yahoo_sp500.csv</t>
+          <t>yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5623,26 +5623,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1386</v>
+        <v>1266</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>yahoo_sp500.xlsx</t>
+          <t>yahoo_smal11.xlsx</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5656,31 +5656,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6029</v>
+        <v>5914</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-09 13:34:29</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.csv</t>
+          <t>yahoo_soja.csv</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5689,97 +5689,97 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>17085</v>
+        <v>1140</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0163</v>
+        <v>0.0011</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:37</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.json</t>
+          <t>yahoo_soja.xlsx</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>56066</v>
+        <v>5835</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0535</v>
+        <v>0.0056</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.parquet</t>
+          <t>yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>31025</v>
+        <v>1386</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0296</v>
+        <v>0.0013</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.xlsx</t>
+          <t>yahoo_sp500.xlsx</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5788,26 +5788,26 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>19037</v>
+        <v>6030</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0182</v>
+        <v>0.0058</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:27:28</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.csv</t>
+          <t>base_yahoo_mensal_larga.csv</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5821,26 +5821,26 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>133378</v>
+        <v>17081</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1272</v>
+        <v>0.0163</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.json</t>
+          <t>base_yahoo_mensal_larga.json</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5854,26 +5854,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>427190</v>
+        <v>56062</v>
       </c>
       <c r="F165" t="n">
-        <v>0.4074</v>
+        <v>0.0535</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.parquet</t>
+          <t>base_yahoo_mensal_larga.parquet</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5887,26 +5887,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>23549</v>
+        <v>31025</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0225</v>
+        <v>0.0296</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.xlsx</t>
+          <t>base_yahoo_mensal_larga.xlsx</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5920,26 +5920,26 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>60817</v>
+        <v>19031</v>
       </c>
       <c r="F167" t="n">
-        <v>0.058</v>
+        <v>0.0181</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.csv</t>
+          <t>base_yahoo_mensal_longa.csv</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5953,26 +5953,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5292</v>
+        <v>133374</v>
       </c>
       <c r="F168" t="n">
-        <v>0.005</v>
+        <v>0.1272</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.json</t>
+          <t>base_yahoo_mensal_longa.json</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5986,26 +5986,26 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>15205</v>
+        <v>427186</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0145</v>
+        <v>0.4074</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.parquet</t>
+          <t>base_yahoo_mensal_longa.parquet</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6019,26 +6019,26 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>9745</v>
+        <v>23554</v>
       </c>
       <c r="F170" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.xlsx</t>
+          <t>base_yahoo_mensal_longa.xlsx</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6052,26 +6052,26 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>7127</v>
+        <v>60808</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0068</v>
+        <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.csv</t>
+          <t>dicionario_variaveis_yahoo.csv</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6085,26 +6085,26 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>826</v>
+        <v>5292</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0008</v>
+        <v>0.005</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.json</t>
+          <t>dicionario_variaveis_yahoo.json</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6118,26 +6118,26 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3314</v>
+        <v>15205</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0032</v>
+        <v>0.0145</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.parquet</t>
+          <t>dicionario_variaveis_yahoo.parquet</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6151,47 +6151,179 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4572</v>
+        <v>9745</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0044</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-09 13:33:38</t>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>7126</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>824</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>3312</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>4574</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>data/final/yahoo/resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>data/final/yahoo</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>.xlsx</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>5571</v>
-      </c>
-      <c r="F175" t="n">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>5564</v>
+      </c>
+      <c r="F179" t="n">
         <v>0.0053</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:33:38</t>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:26:50</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17249</v>
+        <v>17272</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81076</v>
+        <v>81083</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38376</v>
+        <v>38408</v>
       </c>
       <c r="F4" t="n">
         <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19377</v>
+        <v>19388</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173580</v>
+        <v>173882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1655</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>469462</v>
+        <v>470316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4477</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15260</v>
+        <v>16130</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0146</v>
+        <v>0.0154</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55991</v>
+        <v>56078</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0534</v>
+        <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8656</v>
+        <v>8655</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5301</v>
+        <v>5292</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6378</v>
+        <v>6371</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34107</v>
+        <v>34124</v>
       </c>
       <c r="F18" t="n">
         <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161658</v>
+        <v>161659</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71392</v>
+        <v>71424</v>
       </c>
       <c r="F20" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33099</v>
+        <v>33103</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4717</v>
+        <v>4710</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:50</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18445</v>
+        <v>18438</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6839</v>
+        <v>6822</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7791</v>
+        <v>7777</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:27</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22691</v>
+        <v>23264</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0216</v>
+        <v>0.0222</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:32</t>
+          <t>2026-07-11 11:07:02</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12084</v>
+        <v>12218</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:32</t>
+          <t>2026-07-11 11:07:02</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8056</v>
+        <v>8060</v>
       </c>
       <c r="F33" t="n">
         <v>0.0077</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:32</t>
+          <t>2026-07-11 11:07:02</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:32</t>
+          <t>2026-07-11 11:07:02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F39" t="n">
         <v>0.0056</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="F70" t="n">
         <v>0.0009</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5774</v>
+        <v>5786</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="F72" t="n">
         <v>0.0009</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5757</v>
+        <v>5774</v>
       </c>
       <c r="F73" t="n">
         <v>0.0055</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="F74" t="n">
         <v>0.0009</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5764</v>
+        <v>5777</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="F76" t="n">
         <v>0.0009</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5758</v>
+        <v>5774</v>
       </c>
       <c r="F77" t="n">
         <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5979</v>
+        <v>5975</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F94" t="n">
         <v>0.0012</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5985</v>
+        <v>5984</v>
       </c>
       <c r="F95" t="n">
         <v>0.0057</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="F109" t="n">
         <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5915</v>
+        <v>5920</v>
       </c>
       <c r="F119" t="n">
         <v>0.0056</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4369,14 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F120" t="n">
         <v>0.001</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F131" t="n">
         <v>0.0057</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5994</v>
+        <v>5996</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F137" t="n">
         <v>0.0057</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5029,14 +5029,14 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="F140" t="n">
         <v>0.0012</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5995</v>
+        <v>5993</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5161,14 +5161,14 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F144" t="n">
         <v>0.0012</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5425,14 +5425,14 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F152" t="n">
         <v>0.0012</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6015</v>
+        <v>6012</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="F155" t="n">
         <v>0.0057</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="F157" t="n">
         <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5914</v>
+        <v>5918</v>
       </c>
       <c r="F159" t="n">
         <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F160" t="n">
         <v>0.0011</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F161" t="n">
         <v>0.0056</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6030</v>
+        <v>6028</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-10 12:27:28</t>
+          <t>2026-07-11 11:07:51</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17081</v>
+        <v>17075</v>
       </c>
       <c r="F164" t="n">
         <v>0.0163</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>56062</v>
+        <v>56056</v>
       </c>
       <c r="F165" t="n">
         <v>0.0535</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19031</v>
+        <v>19027</v>
       </c>
       <c r="F167" t="n">
         <v>0.0181</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>133374</v>
+        <v>133368</v>
       </c>
       <c r="F168" t="n">
         <v>0.1272</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>427186</v>
+        <v>427180</v>
       </c>
       <c r="F169" t="n">
         <v>0.4074</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23554</v>
+        <v>23512</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60808</v>
+        <v>60806</v>
       </c>
       <c r="F171" t="n">
         <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F176" t="n">
         <v>0.0008</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="F177" t="n">
         <v>0.0032</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5564</v>
+        <v>5565</v>
       </c>
       <c r="F179" t="n">
         <v>0.0053</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-10 12:26:50</t>
+          <t>2026-07-11 11:07:18</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:19</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:19</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:19</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:19</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:19</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56078</v>
+        <v>56081</v>
       </c>
       <c r="F9" t="n">
         <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7014</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6371</v>
+        <v>6370</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34124</v>
+        <v>34126</v>
       </c>
       <c r="F18" t="n">
         <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161659</v>
+        <v>161661</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71424</v>
+        <v>71420</v>
       </c>
       <c r="F20" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33103</v>
+        <v>33101</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4710</v>
+        <v>4712</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:50</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18438</v>
+        <v>18440</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7777</v>
+        <v>7784</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10156</v>
+        <v>10155</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>23264</v>
+        <v>23263</v>
       </c>
       <c r="F30" t="n">
         <v>0.0222</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:02</t>
+          <t>2026-07-12 11:11:51</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12218</v>
+        <v>12221</v>
       </c>
       <c r="F31" t="n">
         <v>0.0117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:02</t>
+          <t>2026-07-12 11:11:51</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8060</v>
+        <v>8059</v>
       </c>
       <c r="F33" t="n">
         <v>0.0077</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:02</t>
+          <t>2026-07-12 11:11:51</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:02</t>
+          <t>2026-07-12 11:11:51</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5873</v>
+        <v>5872</v>
       </c>
       <c r="F37" t="n">
         <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5878</v>
+        <v>5877</v>
       </c>
       <c r="F39" t="n">
         <v>0.0056</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5818</v>
+        <v>5817</v>
       </c>
       <c r="F41" t="n">
         <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="F43" t="n">
         <v>0.0055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5725</v>
+        <v>5724</v>
       </c>
       <c r="F45" t="n">
         <v>0.0055</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5736</v>
+        <v>5735</v>
       </c>
       <c r="F47" t="n">
         <v>0.0055</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5731</v>
+        <v>5730</v>
       </c>
       <c r="F49" t="n">
         <v>0.0055</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5764</v>
+        <v>5763</v>
       </c>
       <c r="F51" t="n">
         <v>0.0055</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5660</v>
+        <v>5659</v>
       </c>
       <c r="F53" t="n">
         <v>0.0054</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="F55" t="n">
         <v>0.0055</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5933</v>
+        <v>5932</v>
       </c>
       <c r="F57" t="n">
         <v>0.0057</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5903</v>
+        <v>5902</v>
       </c>
       <c r="F59" t="n">
         <v>0.0056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5804</v>
+        <v>5803</v>
       </c>
       <c r="F61" t="n">
         <v>0.0055</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5809</v>
+        <v>5808</v>
       </c>
       <c r="F63" t="n">
         <v>0.0055</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5761</v>
+        <v>5760</v>
       </c>
       <c r="F65" t="n">
         <v>0.0055</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5748</v>
+        <v>5747</v>
       </c>
       <c r="F67" t="n">
         <v>0.0055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5751</v>
+        <v>5750</v>
       </c>
       <c r="F69" t="n">
         <v>0.0055</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5786</v>
+        <v>5785</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5774</v>
+        <v>5773</v>
       </c>
       <c r="F73" t="n">
         <v>0.0055</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5777</v>
+        <v>5776</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5774</v>
+        <v>5773</v>
       </c>
       <c r="F77" t="n">
         <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5799</v>
+        <v>5798</v>
       </c>
       <c r="F79" t="n">
         <v>0.0055</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="F81" t="n">
         <v>0.0056</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5910</v>
+        <v>5909</v>
       </c>
       <c r="F83" t="n">
         <v>0.0056</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="F85" t="n">
         <v>0.0056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F87" t="n">
         <v>0.0056</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5690</v>
+        <v>5689</v>
       </c>
       <c r="F89" t="n">
         <v>0.0054</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5818</v>
+        <v>5817</v>
       </c>
       <c r="F91" t="n">
         <v>0.0055</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5975</v>
+        <v>5974</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5984</v>
+        <v>5983</v>
       </c>
       <c r="F95" t="n">
         <v>0.0057</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5944</v>
+        <v>5943</v>
       </c>
       <c r="F97" t="n">
         <v>0.0057</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5894</v>
+        <v>5893</v>
       </c>
       <c r="F99" t="n">
         <v>0.0056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="F101" t="n">
         <v>0.0057</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5940</v>
+        <v>5939</v>
       </c>
       <c r="F105" t="n">
         <v>0.0057</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F107" t="n">
         <v>0.0056</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:21</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="F109" t="n">
         <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5866</v>
+        <v>5865</v>
       </c>
       <c r="F111" t="n">
         <v>0.0056</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="F113" t="n">
         <v>0.0058</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F115" t="n">
         <v>0.0056</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5920</v>
+        <v>5919</v>
       </c>
       <c r="F119" t="n">
         <v>0.0056</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5828</v>
+        <v>5826</v>
       </c>
       <c r="F121" t="n">
         <v>0.0056</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="F123" t="n">
         <v>0.0058</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F127" t="n">
         <v>0.0057</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="F131" t="n">
         <v>0.0057</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F133" t="n">
         <v>0.0057</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5975</v>
+        <v>5974</v>
       </c>
       <c r="F137" t="n">
         <v>0.0057</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5993</v>
+        <v>5992</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5095,14 +5095,14 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F142" t="n">
         <v>0.0012</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="F145" t="n">
         <v>0.0057</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6010</v>
+        <v>6008</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6028</v>
+        <v>6027</v>
       </c>
       <c r="F149" t="n">
         <v>0.0057</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F151" t="n">
         <v>0.0057</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F157" t="n">
         <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F159" t="n">
         <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F160" t="n">
         <v>0.0011</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5836</v>
+        <v>5835</v>
       </c>
       <c r="F161" t="n">
         <v>0.0056</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6028</v>
+        <v>6027</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:51</t>
+          <t>2026-07-12 11:12:20</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17075</v>
+        <v>17077</v>
       </c>
       <c r="F164" t="n">
         <v>0.0163</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>56056</v>
+        <v>56058</v>
       </c>
       <c r="F165" t="n">
         <v>0.0535</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -5887,14 +5887,14 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>31025</v>
+        <v>31021</v>
       </c>
       <c r="F166" t="n">
         <v>0.0296</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19027</v>
+        <v>19026</v>
       </c>
       <c r="F167" t="n">
         <v>0.0181</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>133368</v>
+        <v>133370</v>
       </c>
       <c r="F168" t="n">
         <v>0.1272</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>427180</v>
+        <v>427182</v>
       </c>
       <c r="F169" t="n">
         <v>0.4074</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23512</v>
+        <v>23507</v>
       </c>
       <c r="F170" t="n">
         <v>0.0224</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60806</v>
+        <v>60798</v>
       </c>
       <c r="F171" t="n">
         <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F176" t="n">
         <v>0.0008</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="F177" t="n">
         <v>0.0032</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5565</v>
+        <v>5567</v>
       </c>
       <c r="F179" t="n">
         <v>0.0053</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-11 11:07:18</t>
+          <t>2026-07-12 11:12:06</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17272</v>
+        <v>16466</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0157</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:19</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81083</v>
+        <v>77623</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:19</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38408</v>
+        <v>36454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0348</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:19</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19388</v>
+        <v>18587</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0177</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:19</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173882</v>
+        <v>165285</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.1576</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:19</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470316</v>
+        <v>445159</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.4245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16130</v>
+        <v>14924</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0154</v>
+        <v>0.0142</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56081</v>
+        <v>53235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0535</v>
+        <v>0.0508</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7014</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2141</v>
+        <v>2041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8655</v>
+        <v>8189</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5292</v>
+        <v>5245</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6370</v>
+        <v>6302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34126</v>
+        <v>33304</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0325</v>
+        <v>0.0318</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161661</v>
+        <v>157225</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1499</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71420</v>
+        <v>69337</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33101</v>
+        <v>32248</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.0308</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4712</v>
+        <v>4576</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18440</v>
+        <v>17872</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6822</v>
+        <v>6762</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7784</v>
+        <v>7709</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10155</v>
+        <v>10156</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-12 11:11:51</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12221</v>
+        <v>12247</v>
       </c>
       <c r="F31" t="n">
         <v>0.0117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-12 11:11:51</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10491</v>
+        <v>10192</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>0.0097</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8059</v>
+        <v>7980</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-12 11:11:51</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-12 11:11:51</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="F37" t="n">
         <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5877</v>
+        <v>5878</v>
       </c>
       <c r="F39" t="n">
         <v>0.0056</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="F41" t="n">
         <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="F43" t="n">
         <v>0.0055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="F45" t="n">
         <v>0.0055</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="F47" t="n">
         <v>0.0055</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="F49" t="n">
         <v>0.0055</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="F51" t="n">
         <v>0.0055</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5659</v>
+        <v>5660</v>
       </c>
       <c r="F53" t="n">
         <v>0.0054</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="F55" t="n">
         <v>0.0055</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="F57" t="n">
         <v>0.0057</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="F59" t="n">
         <v>0.0056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:32:44</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="F65" t="n">
         <v>0.0055</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="F67" t="n">
         <v>0.0055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="F69" t="n">
         <v>0.0055</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="F73" t="n">
         <v>0.0055</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="F77" t="n">
         <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5798</v>
+        <v>5799</v>
       </c>
       <c r="F79" t="n">
         <v>0.0055</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="F81" t="n">
         <v>0.0056</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="F83" t="n">
         <v>0.0056</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="F85" t="n">
         <v>0.0056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F87" t="n">
         <v>0.0056</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="F89" t="n">
         <v>0.0054</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="F91" t="n">
         <v>0.0055</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="F95" t="n">
         <v>0.0057</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="F97" t="n">
         <v>0.0057</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="F99" t="n">
         <v>0.0056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="F101" t="n">
         <v>0.0057</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="F105" t="n">
         <v>0.0057</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F107" t="n">
         <v>0.0056</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:21</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F109" t="n">
         <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="F113" t="n">
         <v>0.0058</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5878</v>
+        <v>5881</v>
       </c>
       <c r="F115" t="n">
         <v>0.0056</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="F119" t="n">
         <v>0.0056</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4369,14 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F120" t="n">
         <v>0.001</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="F121" t="n">
         <v>0.0056</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6076</v>
+        <v>6077</v>
       </c>
       <c r="F123" t="n">
         <v>0.0058</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5956</v>
+        <v>5959</v>
       </c>
       <c r="F127" t="n">
         <v>0.0057</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5935</v>
+        <v>5937</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F131" t="n">
         <v>0.0057</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F143" t="n">
         <v>0.0057</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F145" t="n">
         <v>0.0057</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5293,14 +5293,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F148" t="n">
         <v>0.0012</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="F149" t="n">
         <v>0.0057</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6018</v>
+        <v>6020</v>
       </c>
       <c r="F151" t="n">
         <v>0.0057</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F157" t="n">
         <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F159" t="n">
         <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F161" t="n">
         <v>0.0056</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:20</t>
+          <t>2026-07-13 12:33:51</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19026</v>
+        <v>19032</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23507</v>
+        <v>23542</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60798</v>
+        <v>60805</v>
       </c>
       <c r="F171" t="n">
         <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F176" t="n">
         <v>0.0008</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="F177" t="n">
         <v>0.0032</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="F179" t="n">
         <v>0.0053</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-12 11:12:06</t>
+          <t>2026-07-13 12:33:01</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16466</v>
+        <v>17273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0157</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>77623</v>
+        <v>81084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.074</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36454</v>
+        <v>38408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0348</v>
+        <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18587</v>
+        <v>19389</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0177</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>165285</v>
+        <v>173882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1576</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>445159</v>
+        <v>470316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4245</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14924</v>
+        <v>15259</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0142</v>
+        <v>0.0146</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53235</v>
+        <v>56079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0508</v>
+        <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2041</v>
+        <v>2142</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8189</v>
+        <v>8656</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5245</v>
+        <v>5292</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6302</v>
+        <v>6376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33304</v>
+        <v>34119</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0318</v>
+        <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>157225</v>
+        <v>161654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1499</v>
+        <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69337</v>
+        <v>71424</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32248</v>
+        <v>33114</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0308</v>
+        <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4576</v>
+        <v>4705</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17872</v>
+        <v>18433</v>
       </c>
       <c r="F23" t="n">
-        <v>0.017</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6762</v>
+        <v>6821</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7709</v>
+        <v>7768</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:26:25</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12247</v>
+        <v>12215</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0117</v>
+        <v>0.0116</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:26:25</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10192</v>
+        <v>10491</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7980</v>
+        <v>8061</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:26:25</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:26:25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="F37" t="n">
         <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5878</v>
+        <v>5880</v>
       </c>
       <c r="F39" t="n">
         <v>0.0056</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F41" t="n">
         <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F43" t="n">
         <v>0.0055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F45" t="n">
         <v>0.0055</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F47" t="n">
         <v>0.0055</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F49" t="n">
         <v>0.0055</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F51" t="n">
         <v>0.0055</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F53" t="n">
         <v>0.0054</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F55" t="n">
         <v>0.0055</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="F57" t="n">
         <v>0.0057</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="F59" t="n">
         <v>0.0056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5803</v>
+        <v>5805</v>
       </c>
       <c r="F61" t="n">
         <v>0.0055</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5808</v>
+        <v>5810</v>
       </c>
       <c r="F63" t="n">
         <v>0.0055</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:44</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="F65" t="n">
         <v>0.0055</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F67" t="n">
         <v>0.0055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="F69" t="n">
         <v>0.0055</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F73" t="n">
         <v>0.0055</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F77" t="n">
         <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="F79" t="n">
         <v>0.0055</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F81" t="n">
         <v>0.0056</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="F83" t="n">
         <v>0.0056</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F85" t="n">
         <v>0.0056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F87" t="n">
         <v>0.0056</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F89" t="n">
         <v>0.0054</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F91" t="n">
         <v>0.0055</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F94" t="n">
         <v>0.0012</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="F97" t="n">
         <v>0.0057</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="F99" t="n">
         <v>0.0056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F101" t="n">
         <v>0.0057</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F105" t="n">
         <v>0.0057</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F107" t="n">
         <v>0.0056</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -3973,14 +3973,14 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="F108" t="n">
         <v>0.0012</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5939</v>
+        <v>5936</v>
       </c>
       <c r="F109" t="n">
         <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5865</v>
+        <v>5867</v>
       </c>
       <c r="F111" t="n">
         <v>0.0056</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6068</v>
+        <v>6070</v>
       </c>
       <c r="F113" t="n">
         <v>0.0058</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="F115" t="n">
         <v>0.0056</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4369,14 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F120" t="n">
         <v>0.001</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="F121" t="n">
         <v>0.0056</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="F123" t="n">
         <v>0.0058</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F124" t="n">
         <v>0.0013</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="F131" t="n">
         <v>0.0057</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5994</v>
+        <v>5996</v>
       </c>
       <c r="F133" t="n">
         <v>0.0057</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="F137" t="n">
         <v>0.0057</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6006</v>
+        <v>6008</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5029,14 +5029,14 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="F140" t="n">
         <v>0.0012</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="F143" t="n">
         <v>0.0057</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5161,14 +5161,14 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F144" t="n">
         <v>0.0012</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F145" t="n">
         <v>0.0057</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="F149" t="n">
         <v>0.0057</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="F151" t="n">
         <v>0.0057</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6017</v>
+        <v>6019</v>
       </c>
       <c r="F155" t="n">
         <v>0.0057</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6002</v>
+        <v>6004</v>
       </c>
       <c r="F157" t="n">
         <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5918</v>
+        <v>5916</v>
       </c>
       <c r="F159" t="n">
         <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:08</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F160" t="n">
         <v>0.0011</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:51</t>
+          <t>2026-07-14 11:27:09</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17077</v>
+        <v>17069</v>
       </c>
       <c r="F164" t="n">
         <v>0.0163</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>56058</v>
+        <v>56050</v>
       </c>
       <c r="F165" t="n">
         <v>0.0535</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -5887,14 +5887,14 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>31021</v>
+        <v>31025</v>
       </c>
       <c r="F166" t="n">
         <v>0.0296</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19032</v>
+        <v>19027</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>133370</v>
+        <v>133362</v>
       </c>
       <c r="F168" t="n">
         <v>0.1272</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>427182</v>
+        <v>427174</v>
       </c>
       <c r="F169" t="n">
         <v>0.4074</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60805</v>
+        <v>60810</v>
       </c>
       <c r="F171" t="n">
         <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="F176" t="n">
         <v>0.0008</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3312</v>
+        <v>3301</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4574</v>
+        <v>4573</v>
       </c>
       <c r="F178" t="n">
         <v>0.0044</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5568</v>
+        <v>5557</v>
       </c>
       <c r="F179" t="n">
         <v>0.0053</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-13 12:33:01</t>
+          <t>2026-07-14 11:26:41</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:32</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:32</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:32</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:32</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:32</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56079</v>
+        <v>56078</v>
       </c>
       <c r="F9" t="n">
         <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6376</v>
+        <v>6375</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34119</v>
+        <v>34120</v>
       </c>
       <c r="F18" t="n">
         <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161654</v>
+        <v>161655</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33114</v>
+        <v>33113</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18433</v>
+        <v>18434</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6821</v>
+        <v>6818</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7768</v>
+        <v>7771</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F29" t="n">
         <v>0.0097</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:25</t>
+          <t>2026-07-15 11:36:43</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12215</v>
+        <v>12241</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0116</v>
+        <v>0.0117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:25</t>
+          <t>2026-07-15 11:36:43</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:25</t>
+          <t>2026-07-15 11:36:43</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:25</t>
+          <t>2026-07-15 11:36:43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5874</v>
+        <v>5872</v>
       </c>
       <c r="F37" t="n">
         <v>0.0056</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F41" t="n">
         <v>0.0055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5934</v>
+        <v>5933</v>
       </c>
       <c r="F57" t="n">
         <v>0.0057</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="F59" t="n">
         <v>0.0056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F61" t="n">
         <v>0.0055</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F65" t="n">
         <v>0.0055</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F67" t="n">
         <v>0.0055</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F69" t="n">
         <v>0.0055</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F71" t="n">
         <v>0.0055</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F75" t="n">
         <v>0.0055</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5800</v>
+        <v>5799</v>
       </c>
       <c r="F79" t="n">
         <v>0.0055</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F81" t="n">
         <v>0.0056</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="F83" t="n">
         <v>0.0056</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F85" t="n">
         <v>0.0056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F87" t="n">
         <v>0.0056</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F89" t="n">
         <v>0.0054</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F91" t="n">
         <v>0.0055</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F93" t="n">
         <v>0.0057</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5984</v>
+        <v>5983</v>
       </c>
       <c r="F95" t="n">
         <v>0.0057</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="F97" t="n">
         <v>0.0057</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="F99" t="n">
         <v>0.0056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5957</v>
+        <v>5960</v>
       </c>
       <c r="F101" t="n">
         <v>0.0057</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:34</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F105" t="n">
         <v>0.0057</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F107" t="n">
         <v>0.0056</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -3973,14 +3973,14 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="F108" t="n">
         <v>0.0012</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="F109" t="n">
         <v>0.0057</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5867</v>
+        <v>5864</v>
       </c>
       <c r="F111" t="n">
         <v>0.0056</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6070</v>
+        <v>6069</v>
       </c>
       <c r="F113" t="n">
         <v>0.0058</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5897</v>
+        <v>5896</v>
       </c>
       <c r="F117" t="n">
         <v>0.0056</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4303,14 +4303,14 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="F118" t="n">
         <v>0.0012</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5920</v>
+        <v>5915</v>
       </c>
       <c r="F119" t="n">
         <v>0.0056</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5828</v>
+        <v>5827</v>
       </c>
       <c r="F121" t="n">
         <v>0.0056</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="F123" t="n">
         <v>0.0058</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="F124" t="n">
         <v>0.0013</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4633,14 +4633,14 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F128" t="n">
         <v>0.0012</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="F129" t="n">
         <v>0.0057</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F131" t="n">
         <v>0.0057</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F133" t="n">
         <v>0.0057</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F135" t="n">
         <v>0.0057</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F137" t="n">
         <v>0.0057</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F139" t="n">
         <v>0.0057</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F141" t="n">
         <v>0.0057</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="F143" t="n">
         <v>0.0057</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F145" t="n">
         <v>0.0057</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5227,14 +5227,14 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F146" t="n">
         <v>0.0012</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6012</v>
+        <v>6010</v>
       </c>
       <c r="F147" t="n">
         <v>0.0057</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5293,14 +5293,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F148" t="n">
         <v>0.0012</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6029</v>
+        <v>6027</v>
       </c>
       <c r="F149" t="n">
         <v>0.0057</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6021</v>
+        <v>6019</v>
       </c>
       <c r="F151" t="n">
         <v>0.0057</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F155" t="n">
         <v>0.0057</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="F157" t="n">
         <v>0.0057</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="F159" t="n">
         <v>0.0056</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:08</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5836</v>
+        <v>5835</v>
       </c>
       <c r="F161" t="n">
         <v>0.0056</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="F163" t="n">
         <v>0.0058</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-14 11:27:09</t>
+          <t>2026-07-15 11:37:33</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17069</v>
+        <v>17070</v>
       </c>
       <c r="F164" t="n">
         <v>0.0163</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>56050</v>
+        <v>56051</v>
       </c>
       <c r="F165" t="n">
         <v>0.0535</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19027</v>
+        <v>19026</v>
       </c>
       <c r="F167" t="n">
         <v>0.0181</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>133362</v>
+        <v>133363</v>
       </c>
       <c r="F168" t="n">
         <v>0.1272</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>427174</v>
+        <v>427175</v>
       </c>
       <c r="F169" t="n">
         <v>0.4074</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23542</v>
+        <v>23548</v>
       </c>
       <c r="F170" t="n">
         <v>0.0225</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60810</v>
+        <v>60807</v>
       </c>
       <c r="F171" t="n">
         <v>0.058</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4573</v>
+        <v>4569</v>
       </c>
       <c r="F178" t="n">
         <v>0.0044</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5557</v>
+        <v>5560</v>
       </c>
       <c r="F179" t="n">
         <v>0.0053</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-14 11:26:41</t>
+          <t>2026-07-15 11:37:01</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17273</v>
+        <v>16636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0159</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:32</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81084</v>
+        <v>76805</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:32</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38408</v>
+        <v>36606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0349</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:32</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19389</v>
+        <v>18801</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:32</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173882</v>
+        <v>163383</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.1558</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:32</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470316</v>
+        <v>443533</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.423</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15259</v>
+        <v>15020</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0146</v>
+        <v>0.0143</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56078</v>
+        <v>53393</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0535</v>
+        <v>0.0509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2142</v>
+        <v>2034</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8656</v>
+        <v>8182</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5293</v>
+        <v>5258</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6375</v>
+        <v>6311</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34120</v>
+        <v>33473</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0325</v>
+        <v>0.0319</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161655</v>
+        <v>156406</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1492</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71424</v>
+        <v>69481</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33113</v>
+        <v>32483</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.031</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4706</v>
+        <v>4568</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18434</v>
+        <v>17864</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6818</v>
+        <v>6767</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
@@ -1234,64 +1234,64 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7771</v>
+        <v>7710</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_consolidado.csv</t>
+          <t>bcb_sgs_cambio_compra_usd.json</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data/final/documentacao/dicionario_variaveis_consolidado.csv</t>
+          <t>data/final/dashboard/bcb_sgs_cambio_compra_usd.json</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10939</v>
+        <v>51981</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0104</v>
+        <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_consolidado.json</t>
+          <t>bcb_sgs_cambio_venda_usd.json</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data/final/documentacao/dicionario_variaveis_consolidado.json</t>
+          <t>data/final/dashboard/bcb_sgs_cambio_venda_usd.json</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,229 +1300,229 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36702</v>
+        <v>51980</v>
       </c>
       <c r="F27" t="n">
-        <v>0.035</v>
+        <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_consolidado.parquet</t>
+          <t>bcb_sgs_cdi.json</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data/final/documentacao/dicionario_variaveis_consolidado.parquet</t>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13127</v>
+        <v>52174</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0125</v>
+        <v>0.0498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_consolidado.xlsx</t>
+          <t>bcb_sgs_dif_cdi.json</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data/final/documentacao/dicionario_variaveis_consolidado.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10156</v>
+        <v>50988</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0097</v>
+        <v>0.0486</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>lista_arquivos_disponiveis.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data/final/documentacao/lista_arquivos_disponiveis.csv</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>23263</v>
+        <v>48540</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0222</v>
+        <v>0.0463</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-15 11:36:43</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lista_arquivos_disponiveis.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>data/final/documentacao/lista_arquivos_disponiveis.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12241</v>
+        <v>48332</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0117</v>
+        <v>0.0461</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-15 11:36:43</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>lista_series_individuais.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>data/final/documentacao/lista_series_individuais.csv</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10491</v>
+        <v>48619</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>0.0464</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lista_series_individuais.xlsx</t>
+          <t>bcb_sgs_dif_juros_credito_total.json</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>data/final/documentacao/lista_series_individuais.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8061</v>
+        <v>49326</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0077</v>
+        <v>0.047</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>resumo_site.json</t>
+          <t>bcb_sgs_dif_selic_meta.json</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>data/final/documentacao/resumo_site.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1531,31 +1531,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>672</v>
+        <v>48442</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0462</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-15 11:36:43</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ultima_atualizacao.json</t>
+          <t>bcb_sgs_dif_selic_over.json</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>data/final/documentacao/ultima_atualizacao.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>data/final/documentacao</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,1813 +1564,1813 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>289</v>
+        <v>51009</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0003</v>
+        <v>0.0486</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-15 11:36:43</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd.csv</t>
+          <t>bcb_sgs_ibc_br.json</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/dashboard/bcb_sgs_ibc_br.json</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1105</v>
+        <v>50352</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0011</v>
+        <v>0.048</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>bcb_sgs_ibc_br_sa.json</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_ibc_br_sa.json</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5872</v>
+        <v>50264</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0056</v>
+        <v>0.0479</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd.csv</t>
+          <t>bcb_sgs_igp_m.json</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m.json</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>50939</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0011</v>
+        <v>0.0486</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>bcb_sgs_igp_m_acum_12m.json</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m_acum_12m.json</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5880</v>
+        <v>43377</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0056</v>
+        <v>0.0414</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi.csv</t>
+          <t>bcb_sgs_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1226</v>
+        <v>49358</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0012</v>
+        <v>0.0471</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi.xlsx</t>
+          <t>bcb_sgs_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5818</v>
+        <v>49416</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0055</v>
+        <v>0.0471</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi.csv</t>
+          <t>bcb_sgs_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1135</v>
+        <v>49407</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0011</v>
+        <v>0.0471</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi.xlsx</t>
+          <t>bcb_sgs_inpc.json</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_inpc.json</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5813</v>
+        <v>50526</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0055</v>
+        <v>0.0482</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>bcb_sgs_inpc_acum_12m.json</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/dashboard/bcb_sgs_inpc_acum_12m.json</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>954</v>
+        <v>42902</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0009</v>
+        <v>0.0409</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>bcb_sgs_ipca.json</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_ipca.json</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5726</v>
+        <v>50671</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0055</v>
+        <v>0.0483</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>bcb_sgs_ipca_acum_12m.json</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/dashboard/bcb_sgs_ipca_acum_12m.json</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>954</v>
+        <v>42878</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0009</v>
+        <v>0.0409</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>bcb_sgs_juros_credito_total.json</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5737</v>
+        <v>49832</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0055</v>
+        <v>0.0475</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>bcb_sgs_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>958</v>
+        <v>52244</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0009</v>
+        <v>0.0498</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>bcb_sgs_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5732</v>
+        <v>51706</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0055</v>
+        <v>0.0493</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>bcb_sgs_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>958</v>
+        <v>51630</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0009</v>
+        <v>0.0492</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>bcb_sgs_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5765</v>
+        <v>51688</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0055</v>
+        <v>0.0493</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta.csv</t>
+          <t>bcb_sgs_selic_meta.json</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>930</v>
+        <v>50618</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0009</v>
+        <v>0.0483</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>bcb_sgs_selic_over.json</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5661</v>
+        <v>52195</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0054</v>
+        <v>0.0498</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over.csv</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd.json</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_cambio_compra_usd.json</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1135</v>
+        <v>52953</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0011</v>
+        <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over.xlsx</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.json</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_cambio_venda_usd.json</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5813</v>
+        <v>52923</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0055</v>
+        <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br.csv</t>
+          <t>bcb_sgs_var_pct_ibc_br.json</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_ibc_br.json</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>50404</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0012</v>
+        <v>0.0481</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br.xlsx</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa.json</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_ibc_br_sa.json</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5933</v>
+        <v>50241</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0057</v>
+        <v>0.0479</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa.csv</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1215</v>
+        <v>52043</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0012</v>
+        <v>0.0496</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5903</v>
+        <v>50645</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0056</v>
+        <v>0.0483</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>991</v>
+        <v>50989</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0009</v>
+        <v>0.0486</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5804</v>
+        <v>50907</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0055</v>
+        <v>0.0485</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>yahoo_bova11.json</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/dashboard/yahoo_bova11.json</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1008</v>
+        <v>53251</v>
       </c>
       <c r="F62" t="n">
-        <v>0.001</v>
+        <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>yahoo_dolar_real.json</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/dashboard/yahoo_dolar_real.json</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5810</v>
+        <v>52051</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0055</v>
+        <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf.csv</t>
+          <t>yahoo_dow_jones.json</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/dashboard/yahoo_dow_jones.json</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>955</v>
+        <v>54489</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0009</v>
+        <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>yahoo_euro_real.json</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/dashboard/yahoo_euro_real.json</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5761</v>
+        <v>52144</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0055</v>
+        <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj.csv</t>
+          <t>yahoo_ibovespa.json</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/dashboard/yahoo_ibovespa.json</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>952</v>
+        <v>53054</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0009</v>
+        <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>yahoo_ivvb11.json</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/dashboard/yahoo_ivvb11.json</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5748</v>
+        <v>53098</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0055</v>
+        <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total.csv</t>
+          <t>yahoo_milho.json</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/dashboard/yahoo_milho.json</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>954</v>
+        <v>51891</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0009</v>
+        <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>yahoo_nasdaq.json</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/dashboard/yahoo_nasdaq.json</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5751</v>
+        <v>54599</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0055</v>
+        <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc.csv</t>
+          <t>yahoo_ouro.json</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/dashboard/yahoo_ouro.json</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>974</v>
+        <v>53741</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0009</v>
+        <v>0.0513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc.xlsx</t>
+          <t>yahoo_petroleo_brent.json</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/dashboard/yahoo_petroleo_brent.json</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5786</v>
+        <v>53221</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0055</v>
+        <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m.csv</t>
+          <t>yahoo_petroleo_wti.json</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>994</v>
+        <v>53074</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0009</v>
+        <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5775</v>
+        <v>52915</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0055</v>
+        <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca.csv</t>
+          <t>yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>979</v>
+        <v>52901</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0009</v>
+        <v>0.0505</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca.xlsx</t>
+          <t>yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5777</v>
+        <v>52824</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0055</v>
+        <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m.csv</t>
+          <t>yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>990</v>
+        <v>52822</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0009</v>
+        <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5775</v>
+        <v>52893</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0055</v>
+        <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total.csv</t>
+          <t>yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1012</v>
+        <v>52665</v>
       </c>
       <c r="F78" t="n">
-        <v>0.001</v>
+        <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total.xlsx</t>
+          <t>yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5799</v>
+        <v>52909</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0055</v>
+        <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais.csv</t>
+          <t>yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1214</v>
+        <v>52889</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0012</v>
+        <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>yahoo_ret_ouro.json</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5883</v>
+        <v>52871</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0056</v>
+        <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf.csv</t>
+          <t>yahoo_ret_petroleo_brent.json</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1253</v>
+        <v>53075</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0012</v>
+        <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>yahoo_ret_petroleo_wti.json</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5910</v>
+        <v>53042</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0056</v>
+        <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj.csv</t>
+          <t>yahoo_ret_smal11.json</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1253</v>
+        <v>52985</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0012</v>
+        <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>yahoo_ret_soja.json</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/dashboard/yahoo_ret_soja.json</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5895</v>
+        <v>52913</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0056</v>
+        <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total.csv</t>
+          <t>yahoo_ret_sp500.json</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1253</v>
+        <v>52838</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0012</v>
+        <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>yahoo_smal11.json</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/dashboard/yahoo_smal11.json</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5917</v>
+        <v>53171</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0056</v>
+        <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta.csv</t>
+          <t>yahoo_soja.json</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/dashboard/yahoo_soja.json</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1029</v>
+        <v>52338</v>
       </c>
       <c r="F88" t="n">
-        <v>0.001</v>
+        <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta.xlsx</t>
+          <t>yahoo_sp500.json</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/dashboard/yahoo_sp500.json</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/dashboard</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5690</v>
+        <v>54022</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0054</v>
+        <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over.csv</t>
+          <t>dicionario_variaveis_consolidado.csv</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/documentacao/dicionario_variaveis_consolidado.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3379,97 +3379,97 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1226</v>
+        <v>10939</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0012</v>
+        <v>0.0104</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over.xlsx</t>
+          <t>dicionario_variaveis_consolidado.json</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/documentacao/dicionario_variaveis_consolidado.json</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5818</v>
+        <v>36702</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0055</v>
+        <v>0.035</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>dicionario_variaveis_consolidado.parquet</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/documentacao/dicionario_variaveis_consolidado.parquet</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.parquet</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1237</v>
+        <v>13127</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0012</v>
+        <v>0.0125</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>dicionario_variaveis_consolidado.xlsx</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/documentacao/dicionario_variaveis_consolidado.xlsx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3478,31 +3478,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5975</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0057</v>
+        <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>lista_arquivos_disponiveis.csv</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/documentacao/lista_arquivos_disponiveis.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3511,31 +3511,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1237</v>
+        <v>23263</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0012</v>
+        <v>0.0222</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>lista_arquivos_disponiveis.xlsx</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/documentacao/lista_arquivos_disponiveis.xlsx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3544,31 +3544,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5983</v>
+        <v>12252</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0057</v>
+        <v>0.0117</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>lista_dashboards.csv</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/documentacao/lista_dashboards.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3577,31 +3577,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1184</v>
+        <v>11685</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0011</v>
+        <v>0.0111</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>lista_dashboards.xlsx</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/documentacao/lista_dashboards.xlsx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3610,31 +3610,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5944</v>
+        <v>8847</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0057</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>lista_series_individuais.csv</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/documentacao/lista_series_individuais.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3643,31 +3643,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1164</v>
+        <v>10143</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0011</v>
+        <v>0.0097</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>lista_series_individuais.xlsx</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/documentacao/lista_series_individuais.xlsx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3676,92 +3676,92 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5894</v>
+        <v>7986</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0056</v>
+        <v>0.0076</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais.csv</t>
+          <t>resumo_site.json</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
+          <t>data/final/documentacao/resumo_site.json</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1217</v>
+        <v>672</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0012</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+          <t>ultima_atualizacao.json</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
+          <t>data/final/documentacao/ultima_atualizacao.json</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>data/final/series</t>
+          <t>data/final/documentacao</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>.json</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5960</v>
+        <v>289</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0057</v>
+        <v>0.0003</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:34</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3775,26 +3775,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1170</v>
+        <v>1105</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3808,26 +3808,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5918</v>
+        <v>5874</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3841,26 +3841,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1185</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="n">
         <v>0.0011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3874,26 +3874,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5940</v>
+        <v>5880</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3907,26 +3907,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1173</v>
+        <v>1226</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3940,26 +3940,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5917</v>
+        <v>5819</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>yahoo_bova11.csv</t>
+          <t>bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3973,26 +3973,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1307</v>
+        <v>1135</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>yahoo_bova11.xlsx</t>
+          <t>bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4006,26 +4006,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5935</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4039,26 +4039,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1107</v>
+        <v>954</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5864</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4105,26 +4105,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1464</v>
+        <v>954</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0014</v>
+        <v>0.0009</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4138,26 +4138,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6069</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0058</v>
+        <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>yahoo_euro_real.csv</t>
+          <t>bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4171,26 +4171,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1142</v>
+        <v>958</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>yahoo_euro_real.xlsx</t>
+          <t>bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4204,26 +4204,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5880</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa.csv</t>
+          <t>bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4237,26 +4237,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1233</v>
+        <v>958</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa.xlsx</t>
+          <t>bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4270,26 +4270,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5896</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11.csv</t>
+          <t>bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4303,26 +4303,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1266</v>
+        <v>930</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11.xlsx</t>
+          <t>bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4336,26 +4336,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5915</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0056</v>
+        <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>yahoo_milho.csv</t>
+          <t>bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4369,26 +4369,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1080</v>
+        <v>1135</v>
       </c>
       <c r="F120" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>yahoo_milho.xlsx</t>
+          <t>bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4402,26 +4402,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5827</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq.csv</t>
+          <t>bcb_sgs_ibc_br.csv</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4435,26 +4435,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1471</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq.xlsx</t>
+          <t>bcb_sgs_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4468,26 +4468,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6075</v>
+        <v>5934</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>yahoo_ouro.csv</t>
+          <t>bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4501,26 +4501,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1347</v>
+        <v>1215</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>yahoo_ouro.xlsx</t>
+          <t>bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4534,26 +4534,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5915</v>
+        <v>5904</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent.csv</t>
+          <t>bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4567,26 +4567,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1287</v>
+        <v>991</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent.xlsx</t>
+          <t>bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4600,26 +4600,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5959</v>
+        <v>5805</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti.csv</t>
+          <t>bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4633,26 +4633,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1262</v>
+        <v>1008</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti.xlsx</t>
+          <t>bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4666,26 +4666,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5938</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11.csv</t>
+          <t>bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4699,26 +4699,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1242</v>
+        <v>955</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11.xlsx</t>
+          <t>bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4732,26 +4732,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5996</v>
+        <v>5761</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:29:24</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real.csv</t>
+          <t>bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4765,26 +4765,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1240</v>
+        <v>952</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real.xlsx</t>
+          <t>bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4798,26 +4798,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5995</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones.csv</t>
+          <t>bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4831,26 +4831,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1233</v>
+        <v>954</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones.xlsx</t>
+          <t>bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4864,26 +4864,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5994</v>
+        <v>5752</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real.csv</t>
+          <t>bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4897,26 +4897,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1239</v>
+        <v>974</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real.xlsx</t>
+          <t>bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4930,26 +4930,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5976</v>
+        <v>5787</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa.csv</t>
+          <t>bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4963,26 +4963,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1238</v>
+        <v>994</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa.xlsx</t>
+          <t>bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4996,26 +4996,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6007</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11.csv</t>
+          <t>bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5029,26 +5029,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1230</v>
+        <v>979</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11.xlsx</t>
+          <t>bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5062,26 +5062,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5995</v>
+        <v>5778</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho.csv</t>
+          <t>bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5095,26 +5095,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1236</v>
+        <v>990</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho.xlsx</t>
+          <t>bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5128,26 +5128,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6015</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq.csv</t>
+          <t>bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5161,26 +5161,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1238</v>
+        <v>1012</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq.xlsx</t>
+          <t>bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5194,26 +5194,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6014</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro.csv</t>
+          <t>bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5227,26 +5227,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1238</v>
+        <v>1214</v>
       </c>
       <c r="F146" t="n">
         <v>0.0012</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro.xlsx</t>
+          <t>bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5260,26 +5260,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6010</v>
+        <v>5884</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent.csv</t>
+          <t>bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5300,19 +5300,19 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent.xlsx</t>
+          <t>bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5326,26 +5326,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6027</v>
+        <v>5911</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti.csv</t>
+          <t>bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5359,26 +5359,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="F150" t="n">
         <v>0.0012</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti.xlsx</t>
+          <t>bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5392,26 +5392,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6019</v>
+        <v>5896</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11.csv</t>
+          <t>bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5425,26 +5425,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="F152" t="n">
         <v>0.0012</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11.xlsx</t>
+          <t>bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5458,26 +5458,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6015</v>
+        <v>5918</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja.csv</t>
+          <t>bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5491,26 +5491,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1237</v>
+        <v>1029</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja.xlsx</t>
+          <t>bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5524,26 +5524,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6018</v>
+        <v>5691</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0057</v>
+        <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500.csv</t>
+          <t>bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5557,26 +5557,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="F156" t="n">
         <v>0.0012</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500.xlsx</t>
+          <t>bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5590,26 +5590,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6003</v>
+        <v>5819</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0057</v>
+        <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>yahoo_smal11.csv</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5623,26 +5623,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1266</v>
+        <v>1237</v>
       </c>
       <c r="F158" t="n">
         <v>0.0012</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>yahoo_smal11.xlsx</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5656,26 +5656,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5915</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>yahoo_soja.csv</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5689,26 +5689,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1139</v>
+        <v>1237</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>yahoo_soja.xlsx</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5722,26 +5722,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5835</v>
+        <v>5986</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>yahoo_sp500.csv</t>
+          <t>bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5755,26 +5755,26 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1386</v>
+        <v>1184</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0013</v>
+        <v>0.0011</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>yahoo_sp500.xlsx</t>
+          <t>bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5788,31 +5788,31 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6030</v>
+        <v>5945</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:33</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.csv</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5821,97 +5821,97 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17070</v>
+        <v>1164</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0163</v>
+        <v>0.0011</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.json</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>56051</v>
+        <v>5895</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0535</v>
+        <v>0.0056</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.parquet</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>31025</v>
+        <v>1217</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0296</v>
+        <v>0.0012</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_larga.xlsx</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5920,31 +5920,31 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>19026</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0181</v>
+        <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5953,97 +5953,97 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>133363</v>
+        <v>1170</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1272</v>
+        <v>0.0011</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.json</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>427175</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4074</v>
+        <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.parquet</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23548</v>
+        <v>1185</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0225</v>
+        <v>0.0011</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>base_yahoo_mensal_longa.xlsx</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6052,31 +6052,31 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>60807</v>
+        <v>5941</v>
       </c>
       <c r="F171" t="n">
-        <v>0.058</v>
+        <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.csv</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6085,97 +6085,97 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5292</v>
+        <v>1173</v>
       </c>
       <c r="F172" t="n">
-        <v>0.005</v>
+        <v>0.0011</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.json</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>15205</v>
+        <v>5918</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0145</v>
+        <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:47</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.parquet</t>
+          <t>yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>9745</v>
+        <v>1307</v>
       </c>
       <c r="F174" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>dicionario_variaveis_yahoo.xlsx</t>
+          <t>yahoo_bova11.xlsx</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6184,31 +6184,31 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>7126</v>
+        <v>5941</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0068</v>
+        <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.csv</t>
+          <t>yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6217,113 +6217,2291 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>813</v>
+        <v>1107</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0008</v>
+        <v>0.0011</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.json</t>
+          <t>yahoo_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>.json</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3301</v>
+        <v>5864</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0031</v>
+        <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>resumo_disponibilidade_yahoo.parquet</t>
+          <t>yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>data/final/yahoo</t>
+          <t>data/final/series</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>.parquet</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4569</v>
+        <v>1459</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0044</v>
+        <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-15 11:37:01</t>
+          <t>2026-07-15 16:30:46</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>yahoo_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6067</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>yahoo_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1142</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>yahoo_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>5880</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>yahoo_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>yahoo_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>5901</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>yahoo_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1271</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>yahoo_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>5921</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>yahoo_milho.csv</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_milho.csv</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>yahoo_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>5828</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>yahoo_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>1471</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>yahoo_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6077</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>yahoo_ouro.csv</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ouro.csv</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>yahoo_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>5916</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>5961</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>yahoo_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>5938</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>yahoo_ret_bova11.csv</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>yahoo_ret_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>5996</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>5995</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>1233</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>yahoo_ret_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>5996</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>yahoo_ret_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>yahoo_ret_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>5977</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>1238</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>6007</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>5996</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>yahoo_ret_milho.csv</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>1236</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>yahoo_ret_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>6015</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>yahoo_ret_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>yahoo_ret_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>6014</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ouro.csv</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>yahoo_ret_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>6012</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>6020</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>yahoo_ret_smal11.csv</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>yahoo_ret_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>6015</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>yahoo_ret_soja.csv</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1236</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>yahoo_ret_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>6018</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>yahoo_ret_sp500.csv</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>1231</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>yahoo_ret_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>6003</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>yahoo_smal11.csv</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_smal11.csv</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>yahoo_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>5916</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>yahoo_soja.csv</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_soja.csv</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>1139</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>yahoo_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_soja.xlsx</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>5835</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>yahoo_sp500.csv</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_sp500.csv</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>1385</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>yahoo_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>data/final/series</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.csv</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.csv</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>17076</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.json</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.json</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>56057</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.parquet</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.parquet</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>31017</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_larga.xlsx</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_larga.xlsx</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>19027</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.csv</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.csv</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>133369</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.json</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.json</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>427181</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.parquet</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.parquet</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>23496</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>base_yahoo_mensal_longa.xlsx</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/base_yahoo_mensal_longa.xlsx</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>60807</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>5292</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.json</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.json</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>9745</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/dicionario_variaveis_yahoo.xlsx</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>7127</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.csv</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>820</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.json</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>3308</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>data/final/yahoo/resumo_disponibilidade_yahoo.parquet</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>data/final/yahoo</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>.parquet</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>4571</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>data/final/yahoo/resumo_disponibilidade_yahoo.xlsx</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>data/final/yahoo</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>.xlsx</t>
         </is>
       </c>
-      <c r="E179" t="n">
-        <v>5560</v>
-      </c>
-      <c r="F179" t="n">
+      <c r="E245" t="n">
+        <v>5562</v>
+      </c>
+      <c r="F245" t="n">
         <v>0.0053</v>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>2026-07-15 11:37:01</t>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:29:43</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16636</v>
+        <v>17273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0159</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76805</v>
+        <v>81084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0732</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36606</v>
+        <v>38408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0349</v>
+        <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18801</v>
+        <v>19388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0179</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>163383</v>
+        <v>173882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1558</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>443533</v>
+        <v>470316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.423</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15020</v>
+        <v>15259</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0143</v>
+        <v>0.0146</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53393</v>
+        <v>56074</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0509</v>
+        <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2034</v>
+        <v>2142</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8182</v>
+        <v>8656</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5258</v>
+        <v>5292</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6311</v>
+        <v>6373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33473</v>
+        <v>34126</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0319</v>
+        <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>156406</v>
+        <v>161661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1492</v>
+        <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69481</v>
+        <v>71419</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0663</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32483</v>
+        <v>33105</v>
       </c>
       <c r="F21" t="n">
-        <v>0.031</v>
+        <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4568</v>
+        <v>4712</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17864</v>
+        <v>18440</v>
       </c>
       <c r="F23" t="n">
-        <v>0.017</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6767</v>
+        <v>6823</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7710</v>
+        <v>7789</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52051</v>
+        <v>52052</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54489</v>
+        <v>54501</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52144</v>
+        <v>52146</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53054</v>
+        <v>53010</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53098</v>
+        <v>53070</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51891</v>
+        <v>51893</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54599</v>
+        <v>54594</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53741</v>
+        <v>53729</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53221</v>
+        <v>53220</v>
       </c>
       <c r="F71" t="n">
         <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53074</v>
+        <v>53078</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52915</v>
+        <v>52916</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52901</v>
+        <v>52895</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52824</v>
+        <v>52828</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52822</v>
+        <v>52819</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52893</v>
+        <v>52878</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52665</v>
+        <v>52661</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52909</v>
+        <v>52911</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52889</v>
+        <v>52888</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52871</v>
+        <v>52866</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53042</v>
+        <v>53055</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52985</v>
+        <v>52991</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52913</v>
+        <v>52908</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52838</v>
+        <v>52836</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53171</v>
+        <v>53163</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52338</v>
+        <v>52339</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54022</v>
+        <v>54000</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>23263</v>
+        <v>32059</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0222</v>
+        <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:41:24</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>12252</v>
+        <v>15011</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0117</v>
+        <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:41:24</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8847</v>
+        <v>8846</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:48</t>
+          <t>2026-07-16 11:42:11</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10143</v>
+        <v>10491</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7986</v>
+        <v>8060</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:41:24</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:41:24</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5874</v>
+        <v>5873</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5934</v>
+        <v>5933</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:24</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>5799</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5986</v>
+        <v>5985</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="F165" t="n">
         <v>0.0056</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5941</v>
+        <v>5939</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F182" t="n">
         <v>0.0012</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5901</v>
+        <v>5896</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6077</v>
+        <v>6075</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5961</v>
+        <v>5958</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5938</v>
+        <v>5936</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5996</v>
+        <v>5998</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F206" t="n">
         <v>0.0012</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5996</v>
+        <v>5993</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6012</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="F215" t="n">
         <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F216" t="n">
         <v>0.0012</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:47</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:09</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6031</v>
+        <v>6028</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-15 16:30:46</t>
+          <t>2026-07-16 11:42:10</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>31017</v>
+        <v>31020</v>
       </c>
       <c r="F232" t="n">
         <v>0.0296</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19027</v>
+        <v>19026</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23496</v>
+        <v>23540</v>
       </c>
       <c r="F236" t="n">
         <v>0.0224</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60807</v>
+        <v>60800</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3308</v>
+        <v>3310</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4571</v>
+        <v>4574</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5562</v>
+        <v>5569</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-15 16:29:43</t>
+          <t>2026-07-16 11:41:41</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17273</v>
+        <v>17272</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81084</v>
+        <v>81083</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19388</v>
+        <v>19389</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15259</v>
+        <v>15258</v>
       </c>
       <c r="F8" t="n">
         <v>0.0146</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56074</v>
+        <v>56077</v>
       </c>
       <c r="F9" t="n">
         <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8656</v>
+        <v>8655</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6373</v>
+        <v>6374</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34126</v>
+        <v>34128</v>
       </c>
       <c r="F18" t="n">
         <v>0.0325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161661</v>
+        <v>161663</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71419</v>
+        <v>71424</v>
       </c>
       <c r="F20" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33105</v>
+        <v>33108</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4712</v>
+        <v>4714</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18440</v>
+        <v>18442</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6823</v>
+        <v>6837</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7789</v>
+        <v>7778</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51981</v>
+        <v>51975</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51980</v>
+        <v>51976</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52953</v>
+        <v>52960</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52923</v>
+        <v>52919</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53251</v>
+        <v>53253</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52052</v>
+        <v>52048</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54501</v>
+        <v>54507</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53010</v>
+        <v>53006</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53070</v>
+        <v>53080</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51893</v>
+        <v>51915</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54594</v>
+        <v>54589</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53729</v>
+        <v>53739</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53078</v>
+        <v>53068</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52916</v>
+        <v>52914</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52895</v>
+        <v>52902</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52828</v>
+        <v>52824</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52878</v>
+        <v>52889</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52661</v>
+        <v>52663</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52911</v>
+        <v>52917</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52888</v>
+        <v>52898</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52866</v>
+        <v>52865</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53075</v>
+        <v>53082</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53055</v>
+        <v>53057</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52991</v>
+        <v>52980</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52908</v>
+        <v>52913</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52836</v>
+        <v>52838</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53163</v>
+        <v>53138</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52339</v>
+        <v>52338</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54000</v>
+        <v>54022</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32059</v>
+        <v>32060</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:24</t>
+          <t>2026-07-17 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15011</v>
+        <v>15010</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:24</t>
+          <t>2026-07-17 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:11</t>
+          <t>2026-07-17 11:23:39</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:24</t>
+          <t>2026-07-17 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:24</t>
+          <t>2026-07-17 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F160" t="n">
         <v>0.0012</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5985</v>
+        <v>5983</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:38</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5939</v>
+        <v>5936</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5936</v>
+        <v>5938</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5998</v>
+        <v>5994</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F206" t="n">
         <v>0.0012</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F212" t="n">
         <v>0.0012</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6010</v>
+        <v>6008</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:09</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5836</v>
+        <v>5834</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6028</v>
+        <v>6030</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-16 11:42:10</t>
+          <t>2026-07-17 11:23:37</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17076</v>
+        <v>17079</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:14</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56057</v>
+        <v>56060</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>31020</v>
+        <v>31025</v>
       </c>
       <c r="F232" t="n">
         <v>0.0296</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19026</v>
+        <v>19033</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133369</v>
+        <v>133372</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427181</v>
+        <v>427184</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23540</v>
+        <v>23548</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60800</v>
+        <v>60804</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3310</v>
+        <v>3308</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5569</v>
+        <v>5564</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-16 11:41:41</t>
+          <t>2026-07-17 11:23:15</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17272</v>
+        <v>17311</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:57</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81083</v>
+        <v>81106</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:57</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38408</v>
+        <v>38440</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:57</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19389</v>
+        <v>19421</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:57</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173882</v>
+        <v>174258</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:57</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470316</v>
+        <v>471244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15258</v>
+        <v>15522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0146</v>
+        <v>0.0148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56077</v>
+        <v>56201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0535</v>
+        <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8655</v>
+        <v>8654</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5292</v>
+        <v>5279</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6374</v>
+        <v>6360</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34128</v>
+        <v>34169</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0325</v>
+        <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161663</v>
+        <v>161688</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71424</v>
+        <v>71452</v>
       </c>
       <c r="F20" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33108</v>
+        <v>33131</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4714</v>
+        <v>4715</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18442</v>
+        <v>18443</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6837</v>
+        <v>6801</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7778</v>
+        <v>7762</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51975</v>
+        <v>51953</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0496</v>
+        <v>0.0495</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51976</v>
+        <v>51950</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0496</v>
+        <v>0.0495</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1597,14 +1597,14 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>50352</v>
+        <v>51210</v>
       </c>
       <c r="F36" t="n">
-        <v>0.048</v>
+        <v>0.0488</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>50264</v>
+        <v>51073</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0479</v>
+        <v>0.0487</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52960</v>
+        <v>52951</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52919</v>
+        <v>52914</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2257,14 +2257,14 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>50404</v>
+        <v>51219</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0481</v>
+        <v>0.0488</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>50241</v>
+        <v>51073</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0479</v>
+        <v>0.0487</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53253</v>
+        <v>53245</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52048</v>
+        <v>52052</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54507</v>
+        <v>54519</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52146</v>
+        <v>52142</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53006</v>
+        <v>53008</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53080</v>
+        <v>53098</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51915</v>
+        <v>51912</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54589</v>
+        <v>54600</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53220</v>
+        <v>53201</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53068</v>
+        <v>53081</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52914</v>
+        <v>52909</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52902</v>
+        <v>52895</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52824</v>
+        <v>52846</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52819</v>
+        <v>52815</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52889</v>
+        <v>52886</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52663</v>
+        <v>52665</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52917</v>
+        <v>52913</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52898</v>
+        <v>52896</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52865</v>
+        <v>52862</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53082</v>
+        <v>53086</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53057</v>
+        <v>53060</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52980</v>
+        <v>52988</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52913</v>
+        <v>52908</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52838</v>
+        <v>52853</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53138</v>
+        <v>53147</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52338</v>
+        <v>52339</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54022</v>
+        <v>54029</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-17 11:22:59</t>
+          <t>2026-07-18 11:05:06</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15010</v>
+        <v>15030</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-17 11:22:59</t>
+          <t>2026-07-18 11:05:06</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8846</v>
+        <v>8842</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:39</t>
+          <t>2026-07-18 11:06:00</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8060</v>
+        <v>8055</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-17 11:22:59</t>
+          <t>2026-07-18 11:05:06</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-17 11:22:59</t>
+          <t>2026-07-18 11:05:06</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4435,14 +4435,14 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F122" t="n">
         <v>0.0012</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5933</v>
+        <v>5946</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="F124" t="n">
         <v>0.0012</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5903</v>
+        <v>5923</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F160" t="n">
         <v>0.0012</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5983</v>
+        <v>5985</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5755,14 +5755,14 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1184</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="n">
         <v>0.0011</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5944</v>
+        <v>5962</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1164</v>
+        <v>1189</v>
       </c>
       <c r="F164" t="n">
         <v>0.0011</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5894</v>
+        <v>5930</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:59</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:38</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5865</v>
+        <v>5867</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5879</v>
+        <v>5881</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5921</v>
+        <v>5919</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5959</v>
+        <v>5961</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F200" t="n">
         <v>0.0012</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6008</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5834</v>
+        <v>5837</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:37</t>
+          <t>2026-07-18 11:05:58</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17079</v>
+        <v>17081</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:14</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56060</v>
+        <v>56062</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>31025</v>
+        <v>31021</v>
       </c>
       <c r="F232" t="n">
         <v>0.0296</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19033</v>
+        <v>19023</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133372</v>
+        <v>133374</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427184</v>
+        <v>427186</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23548</v>
+        <v>23546</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60804</v>
+        <v>60793</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5564</v>
+        <v>5569</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-17 11:23:15</t>
+          <t>2026-07-18 11:05:28</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:57</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:57</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:57</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19421</v>
+        <v>19420</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:57</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:57</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56201</v>
+        <v>56197</v>
       </c>
       <c r="F9" t="n">
         <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6360</v>
+        <v>6359</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51912</v>
+        <v>51905</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53081</v>
+        <v>53084</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:11</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52913</v>
+        <v>52912</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52862</v>
+        <v>52869</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53060</v>
+        <v>53057</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52908</v>
+        <v>52907</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52339</v>
+        <v>52337</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32060</v>
+        <v>32061</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:06</t>
+          <t>2026-07-19 11:09:27</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15030</v>
+        <v>15031</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:06</t>
+          <t>2026-07-19 11:09:27</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-18 11:06:00</t>
+          <t>2026-07-19 11:10:12</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8055</v>
+        <v>8054</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:06</t>
+          <t>2026-07-19 11:09:27</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:06</t>
+          <t>2026-07-19 11:09:27</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5873</v>
+        <v>5872</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>5799</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5985</v>
+        <v>5984</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5930</v>
+        <v>5929</v>
       </c>
       <c r="F165" t="n">
         <v>0.0057</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:59</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5867</v>
+        <v>5866</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6067</v>
+        <v>6066</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6018</v>
+        <v>6016</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:09</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5837</v>
+        <v>5836</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:58</t>
+          <t>2026-07-19 11:10:10</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19023</v>
+        <v>19026</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23546</v>
+        <v>23544</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60793</v>
+        <v>60790</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:45</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-18 11:05:28</t>
+          <t>2026-07-19 11:09:46</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:45</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:45</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:45</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19420</v>
+        <v>19421</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:45</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:45</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56197</v>
+        <v>56201</v>
       </c>
       <c r="F9" t="n">
         <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34169</v>
+        <v>34165</v>
       </c>
       <c r="F18" t="n">
         <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161688</v>
+        <v>161684</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33131</v>
+        <v>33126</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4715</v>
+        <v>4711</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18443</v>
+        <v>18439</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6801</v>
+        <v>6798</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7762</v>
+        <v>7760</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52052</v>
+        <v>52045</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52142</v>
+        <v>52140</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51905</v>
+        <v>51916</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53739</v>
+        <v>53737</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53201</v>
+        <v>53218</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53084</v>
+        <v>53076</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52895</v>
+        <v>52901</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:11</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52815</v>
+        <v>52813</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52912</v>
+        <v>52909</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53086</v>
+        <v>53088</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53057</v>
+        <v>53060</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52907</v>
+        <v>52913</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52337</v>
+        <v>52336</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:27</t>
+          <t>2026-07-20 12:17:39</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15031</v>
+        <v>15029</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:27</t>
+          <t>2026-07-20 12:17:39</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:12</t>
+          <t>2026-07-20 12:18:48</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8054</v>
+        <v>8055</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:27</t>
+          <t>2026-07-20 12:17:39</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:27</t>
+          <t>2026-07-20 12:17:39</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:47</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F190" t="n">
         <v>0.0013</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5916</v>
+        <v>5914</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:09</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5836</v>
+        <v>5835</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-19 11:10:10</t>
+          <t>2026-07-20 12:18:46</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17081</v>
+        <v>17077</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:55</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56062</v>
+        <v>56058</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:55</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:55</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19026</v>
+        <v>19022</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:55</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133374</v>
+        <v>133370</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:55</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427186</v>
+        <v>427182</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23544</v>
+        <v>23552</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60790</v>
+        <v>60792</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:45</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3306</v>
+        <v>3302</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4574</v>
+        <v>4570</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5570</v>
+        <v>5564</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-19 11:09:46</t>
+          <t>2026-07-20 12:17:56</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17311</v>
+        <v>17312</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:45</t>
+          <t>2026-07-21 11:48:09</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81106</v>
+        <v>81107</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:45</t>
+          <t>2026-07-21 11:48:09</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:45</t>
+          <t>2026-07-21 11:48:09</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:45</t>
+          <t>2026-07-21 11:48:09</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174258</v>
+        <v>174259</v>
       </c>
       <c r="F6" t="n">
         <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:45</t>
+          <t>2026-07-21 11:48:09</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471244</v>
+        <v>471245</v>
       </c>
       <c r="F7" t="n">
         <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56201</v>
+        <v>56197</v>
       </c>
       <c r="F9" t="n">
         <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8654</v>
+        <v>8655</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34165</v>
+        <v>34170</v>
       </c>
       <c r="F18" t="n">
         <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161684</v>
+        <v>161689</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71452</v>
+        <v>71456</v>
       </c>
       <c r="F20" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33126</v>
+        <v>33132</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4711</v>
+        <v>4716</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18439</v>
+        <v>18444</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6798</v>
+        <v>6804</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7760</v>
+        <v>7749</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51953</v>
+        <v>51977</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0495</v>
+        <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51950</v>
+        <v>51976</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0495</v>
+        <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52951</v>
+        <v>52958</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52914</v>
+        <v>52923</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53245</v>
+        <v>53241</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52045</v>
+        <v>52054</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54519</v>
+        <v>54512</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52140</v>
+        <v>52144</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53008</v>
+        <v>53012</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53098</v>
+        <v>53099</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51916</v>
+        <v>51910</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53737</v>
+        <v>53739</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53218</v>
+        <v>53212</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53076</v>
+        <v>53083</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52909</v>
+        <v>52910</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52901</v>
+        <v>52898</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52846</v>
+        <v>52848</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52813</v>
+        <v>52821</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52886</v>
+        <v>52880</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52665</v>
+        <v>52661</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52909</v>
+        <v>52911</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52896</v>
+        <v>52898</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52869</v>
+        <v>52864</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53088</v>
+        <v>53085</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53060</v>
+        <v>53062</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52988</v>
+        <v>52979</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52913</v>
+        <v>52908</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52853</v>
+        <v>52851</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53147</v>
+        <v>53159</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52336</v>
+        <v>52342</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54029</v>
+        <v>54026</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:39</t>
+          <t>2026-07-21 11:47:30</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15029</v>
+        <v>15024</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:39</t>
+          <t>2026-07-21 11:47:30</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:48</t>
+          <t>2026-07-21 11:48:12</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8055</v>
+        <v>8054</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:39</t>
+          <t>2026-07-21 11:47:30</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:39</t>
+          <t>2026-07-21 11:47:30</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:11</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:47</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5866</v>
+        <v>5864</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5828</v>
+        <v>5827</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="F190" t="n">
         <v>0.0013</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F198" t="n">
         <v>0.0012</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6008</v>
+        <v>6005</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F212" t="n">
         <v>0.0012</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6028</v>
+        <v>6030</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-20 12:18:46</t>
+          <t>2026-07-21 11:48:10</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17077</v>
+        <v>17081</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:55</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56058</v>
+        <v>56062</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:55</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>31021</v>
+        <v>31025</v>
       </c>
       <c r="F232" t="n">
         <v>0.0296</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:55</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19022</v>
+        <v>19028</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:55</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133370</v>
+        <v>133374</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:55</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427182</v>
+        <v>427186</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23552</v>
+        <v>23553</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60792</v>
+        <v>60802</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3302</v>
+        <v>3310</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4570</v>
+        <v>4574</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-20 12:17:56</t>
+          <t>2026-07-21 11:47:51</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17312</v>
+        <v>17311</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:09</t>
+          <t>2026-07-22 11:49:12</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81107</v>
+        <v>81106</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:09</t>
+          <t>2026-07-22 11:49:12</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:09</t>
+          <t>2026-07-22 11:49:12</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19421</v>
+        <v>19420</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:09</t>
+          <t>2026-07-22 11:49:12</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174259</v>
+        <v>174258</v>
       </c>
       <c r="F6" t="n">
         <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:09</t>
+          <t>2026-07-22 11:49:12</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471245</v>
+        <v>471244</v>
       </c>
       <c r="F7" t="n">
         <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8655</v>
+        <v>8654</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33132</v>
+        <v>33128</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6804</v>
+        <v>6801</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7749</v>
+        <v>7753</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51977</v>
+        <v>51972</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51976</v>
+        <v>51971</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52958</v>
+        <v>52953</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52923</v>
+        <v>52918</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53241</v>
+        <v>53239</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52054</v>
+        <v>52051</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54512</v>
+        <v>54507</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52144</v>
+        <v>52146</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53012</v>
+        <v>53016</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53099</v>
+        <v>53100</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51910</v>
+        <v>51909</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53212</v>
+        <v>53222</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53083</v>
+        <v>53082</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52910</v>
+        <v>52912</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52848</v>
+        <v>52842</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52821</v>
+        <v>52823</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52880</v>
+        <v>52887</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52661</v>
+        <v>52665</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52898</v>
+        <v>52894</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52864</v>
+        <v>52869</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53085</v>
+        <v>53080</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53062</v>
+        <v>53064</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52979</v>
+        <v>52981</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52908</v>
+        <v>52903</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52851</v>
+        <v>52835</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53159</v>
+        <v>53169</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52342</v>
+        <v>52341</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54026</v>
+        <v>54022</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:30</t>
+          <t>2026-07-22 11:48:29</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15024</v>
+        <v>15012</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:30</t>
+          <t>2026-07-22 11:48:29</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:12</t>
+          <t>2026-07-22 11:49:15</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8054</v>
+        <v>8055</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:30</t>
+          <t>2026-07-22 11:48:29</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:30</t>
+          <t>2026-07-22 11:48:29</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3841,14 +3841,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F104" t="n">
         <v>0.0011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:11</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:14</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F176" t="n">
         <v>0.0011</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5919</v>
+        <v>5916</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6077</v>
+        <v>6075</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5915</v>
+        <v>5918</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5938</v>
+        <v>5936</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F198" t="n">
         <v>0.0012</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6005</v>
+        <v>6007</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6019</v>
+        <v>6017</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6030</v>
+        <v>6028</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-21 11:48:10</t>
+          <t>2026-07-22 11:49:13</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17081</v>
+        <v>17082</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56062</v>
+        <v>56063</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19028</v>
+        <v>19030</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133374</v>
+        <v>133375</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427186</v>
+        <v>427187</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23553</v>
+        <v>23555</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60802</v>
+        <v>60807</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-21 11:47:51</t>
+          <t>2026-07-22 11:48:45</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17311</v>
+        <v>17312</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:12</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81106</v>
+        <v>81107</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:12</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:12</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:12</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174258</v>
+        <v>174259</v>
       </c>
       <c r="F6" t="n">
         <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:12</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471244</v>
+        <v>471245</v>
       </c>
       <c r="F7" t="n">
         <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15522</v>
+        <v>15190</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0148</v>
+        <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56197</v>
+        <v>56195</v>
       </c>
       <c r="F9" t="n">
         <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8654</v>
+        <v>8655</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34170</v>
+        <v>34163</v>
       </c>
       <c r="F18" t="n">
         <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161689</v>
+        <v>161682</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33128</v>
+        <v>33140</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4716</v>
+        <v>4709</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18444</v>
+        <v>18437</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6801</v>
+        <v>6809</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51972</v>
+        <v>51977</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51971</v>
+        <v>51976</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52953</v>
+        <v>52958</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52918</v>
+        <v>52921</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53239</v>
+        <v>53233</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52051</v>
+        <v>52047</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54507</v>
+        <v>54519</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52146</v>
+        <v>52144</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53016</v>
+        <v>53002</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0506</v>
+        <v>0.0505</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53100</v>
+        <v>53096</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51909</v>
+        <v>51918</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54600</v>
+        <v>54602</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53739</v>
+        <v>53731</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53222</v>
+        <v>53215</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53082</v>
+        <v>53058</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52912</v>
+        <v>52917</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52898</v>
+        <v>52893</v>
       </c>
       <c r="F74" t="n">
         <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52842</v>
+        <v>52843</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52823</v>
+        <v>52816</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52887</v>
+        <v>52883</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52665</v>
+        <v>52661</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52911</v>
+        <v>52910</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52894</v>
+        <v>52898</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52869</v>
+        <v>52871</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53080</v>
+        <v>53078</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52981</v>
+        <v>52984</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52903</v>
+        <v>52922</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52835</v>
+        <v>52850</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53169</v>
+        <v>53146</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52341</v>
+        <v>52343</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54022</v>
+        <v>54027</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:29</t>
+          <t>2026-07-23 11:51:14</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15012</v>
+        <v>15059</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0143</v>
+        <v>0.0144</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:29</t>
+          <t>2026-07-23 11:51:14</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8843</v>
+        <v>8842</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:15</t>
+          <t>2026-07-23 11:52:02</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8055</v>
+        <v>8054</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:29</t>
+          <t>2026-07-23 11:51:14</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:29</t>
+          <t>2026-07-23 11:51:14</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3841,14 +3841,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="n">
         <v>0.0011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5975</v>
+        <v>5974</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5984</v>
+        <v>5986</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:14</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F176" t="n">
         <v>0.0011</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5916</v>
+        <v>5919</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5918</v>
+        <v>5915</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5936</v>
+        <v>5938</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5996</v>
+        <v>5994</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F214" t="n">
         <v>0.0012</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6030</v>
+        <v>6028</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:01</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6028</v>
+        <v>6027</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-22 11:49:13</t>
+          <t>2026-07-23 11:52:00</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17082</v>
+        <v>17074</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:32</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56063</v>
+        <v>56055</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:32</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:32</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19030</v>
+        <v>19040</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:32</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133375</v>
+        <v>133367</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:32</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427187</v>
+        <v>427179</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23555</v>
+        <v>23551</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60807</v>
+        <v>60794</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3309</v>
+        <v>3302</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4574</v>
+        <v>4573</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5564</v>
+        <v>5569</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-22 11:48:45</t>
+          <t>2026-07-23 11:51:33</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19420</v>
+        <v>19421</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15190</v>
+        <v>15522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0145</v>
+        <v>0.0148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56195</v>
+        <v>56196</v>
       </c>
       <c r="F9" t="n">
         <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6359</v>
+        <v>6362</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34163</v>
+        <v>34164</v>
       </c>
       <c r="F18" t="n">
         <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161682</v>
+        <v>161683</v>
       </c>
       <c r="F19" t="n">
         <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33140</v>
+        <v>33130</v>
       </c>
       <c r="F21" t="n">
         <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4709</v>
+        <v>4710</v>
       </c>
       <c r="F22" t="n">
         <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18437</v>
+        <v>18438</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6809</v>
+        <v>6802</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51977</v>
+        <v>51976</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51976</v>
+        <v>51975</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52958</v>
+        <v>52957</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52921</v>
+        <v>52916</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53233</v>
+        <v>53251</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52047</v>
+        <v>52054</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54519</v>
+        <v>54521</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53002</v>
+        <v>53026</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0505</v>
+        <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53096</v>
+        <v>53102</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51918</v>
+        <v>51908</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54602</v>
+        <v>54591</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53731</v>
+        <v>53740</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0512</v>
+        <v>0.0513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53215</v>
+        <v>53206</v>
       </c>
       <c r="F71" t="n">
         <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53058</v>
+        <v>53084</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52917</v>
+        <v>52910</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52893</v>
+        <v>52900</v>
       </c>
       <c r="F74" t="n">
         <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52843</v>
+        <v>52838</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52816</v>
+        <v>52823</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52883</v>
+        <v>52891</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52661</v>
+        <v>52658</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52910</v>
+        <v>52905</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52898</v>
+        <v>52892</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52871</v>
+        <v>52864</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53078</v>
+        <v>53082</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:51</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53064</v>
+        <v>53067</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52984</v>
+        <v>52977</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52850</v>
+        <v>52847</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53146</v>
+        <v>53149</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52343</v>
+        <v>52347</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:14</t>
+          <t>2026-07-24 11:42:59</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15059</v>
+        <v>15026</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0144</v>
+        <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:14</t>
+          <t>2026-07-24 11:42:59</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:02</t>
+          <t>2026-07-24 11:43:52</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8054</v>
+        <v>8055</v>
       </c>
       <c r="F99" t="n">
         <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:14</t>
+          <t>2026-07-24 11:42:59</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:14</t>
+          <t>2026-07-24 11:42:59</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5986</v>
+        <v>5985</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="F165" t="n">
         <v>0.0057</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5936</v>
+        <v>5942</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:49</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5919</v>
+        <v>5921</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5915</v>
+        <v>5918</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="F192" t="n">
         <v>0.0012</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6006</v>
+        <v>6008</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6010</v>
+        <v>6012</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="F214" t="n">
         <v>0.0012</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="F215" t="n">
         <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6020</v>
+        <v>6022</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6014</v>
+        <v>6016</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6018</v>
+        <v>6020</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:01</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6027</v>
+        <v>6029</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-23 11:52:00</t>
+          <t>2026-07-24 11:43:50</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17074</v>
+        <v>17075</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:32</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56055</v>
+        <v>56056</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:32</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:32</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19040</v>
+        <v>19028</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:32</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133367</v>
+        <v>133368</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:32</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427179</v>
+        <v>427180</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23551</v>
+        <v>23554</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60794</v>
+        <v>60804</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="F243" t="n">
         <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4573</v>
+        <v>4574</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5569</v>
+        <v>5561</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-23 11:51:33</t>
+          <t>2026-07-24 11:43:17</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17312</v>
+        <v>16296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81107</v>
+        <v>78028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38440</v>
+        <v>36619</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0367</v>
+        <v>0.0349</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19421</v>
+        <v>18972</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0181</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174259</v>
+        <v>166946</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1662</v>
+        <v>0.1592</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471245</v>
+        <v>447096</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4494</v>
+        <v>0.4264</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15522</v>
+        <v>15122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0148</v>
+        <v>0.0144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56196</v>
+        <v>53308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0536</v>
+        <v>0.0508</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2141</v>
+        <v>2041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8655</v>
+        <v>8189</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5279</v>
+        <v>5266</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6362</v>
+        <v>6316</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34164</v>
+        <v>33138</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0326</v>
+        <v>0.0316</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161683</v>
+        <v>157634</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1503</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71456</v>
+        <v>69518</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33130</v>
+        <v>32617</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.0311</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4710</v>
+        <v>4584</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18438</v>
+        <v>17880</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.0171</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6802</v>
+        <v>6749</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7754</v>
+        <v>7707</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51976</v>
+        <v>51969</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51975</v>
+        <v>51968</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52957</v>
+        <v>52956</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52916</v>
+        <v>52923</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53251</v>
+        <v>53234</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54521</v>
+        <v>54514</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52144</v>
+        <v>52139</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51908</v>
+        <v>51912</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54591</v>
+        <v>54600</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53740</v>
+        <v>53732</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53206</v>
+        <v>53208</v>
       </c>
       <c r="F71" t="n">
         <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53084</v>
+        <v>53082</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52910</v>
+        <v>52917</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52838</v>
+        <v>52836</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52823</v>
+        <v>52821</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52891</v>
+        <v>52888</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52658</v>
+        <v>52660</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52905</v>
+        <v>52915</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52892</v>
+        <v>52901</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52864</v>
+        <v>52869</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53082</v>
+        <v>53090</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:51</t>
+          <t>2026-07-25 11:12:56</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53067</v>
+        <v>53066</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52977</v>
+        <v>52984</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52922</v>
+        <v>52921</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52847</v>
+        <v>52850</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53149</v>
+        <v>53157</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52347</v>
+        <v>52345</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54027</v>
+        <v>54028</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-24 11:42:59</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15026</v>
+        <v>15011</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-24 11:42:59</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:52</t>
+          <t>2026-07-25 11:12:57</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10491</v>
+        <v>10199</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01</v>
+        <v>0.0097</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8055</v>
+        <v>7973</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-24 11:42:59</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-24 11:42:59</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5874</v>
+        <v>5872</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:11:46</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>5799</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5985</v>
+        <v>5984</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5930</v>
+        <v>5929</v>
       </c>
       <c r="F165" t="n">
         <v>0.0057</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5942</v>
+        <v>5935</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6068</v>
+        <v>6066</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:54</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:49</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5921</v>
+        <v>5918</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5829</v>
+        <v>5828</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5918</v>
+        <v>5915</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="F192" t="n">
         <v>0.0012</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5996</v>
+        <v>5993</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6015</v>
+        <v>6013</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6012</v>
+        <v>6009</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6022</v>
+        <v>6019</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6016</v>
+        <v>6013</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6020</v>
+        <v>6018</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6002</v>
+        <v>6004</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:50</t>
+          <t>2026-07-25 11:12:55</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17075</v>
+        <v>17081</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:02</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56056</v>
+        <v>56062</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19028</v>
+        <v>19030</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133368</v>
+        <v>133374</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427180</v>
+        <v>427186</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23554</v>
+        <v>23553</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60804</v>
+        <v>60798</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3301</v>
+        <v>3306</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-24 11:43:17</t>
+          <t>2026-07-25 11:12:03</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16296</v>
+        <v>17311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0155</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>78028</v>
+        <v>81106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36619</v>
+        <v>38440</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0349</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18972</v>
+        <v>19421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>166946</v>
+        <v>174258</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1592</v>
+        <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>447096</v>
+        <v>471244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4264</v>
+        <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15122</v>
+        <v>15522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0144</v>
+        <v>0.0148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53308</v>
+        <v>56193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0508</v>
+        <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2041</v>
+        <v>2140</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8189</v>
+        <v>8654</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5266</v>
+        <v>5279</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6316</v>
+        <v>6361</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33138</v>
+        <v>34173</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0316</v>
+        <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>157634</v>
+        <v>161692</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1503</v>
+        <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69518</v>
+        <v>71456</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0663</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32617</v>
+        <v>33133</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0311</v>
+        <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4584</v>
+        <v>4719</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17880</v>
+        <v>18447</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0171</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6749</v>
+        <v>6804</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7707</v>
+        <v>7761</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0073</v>
+        <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54514</v>
+        <v>54521</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51912</v>
+        <v>51918</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54600</v>
+        <v>54591</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53732</v>
+        <v>53739</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52836</v>
+        <v>52838</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52888</v>
+        <v>52891</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52915</v>
+        <v>52909</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52901</v>
+        <v>52892</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52869</v>
+        <v>52871</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:56</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52921</v>
+        <v>52918</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52850</v>
+        <v>52847</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52345</v>
+        <v>52343</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54028</v>
+        <v>54027</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32061</v>
+        <v>32063</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:20:34</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15011</v>
+        <v>15003</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:20:34</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8843</v>
+        <v>8842</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:57</t>
+          <t>2026-07-26 11:22:08</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10199</v>
+        <v>10491</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7973</v>
+        <v>8054</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:20:34</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:20:34</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-25 11:11:46</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:07</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:54</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5897</v>
+        <v>5895</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6009</v>
+        <v>6011</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5836</v>
+        <v>5835</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:55</t>
+          <t>2026-07-26 11:22:06</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17081</v>
+        <v>17085</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:02</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56062</v>
+        <v>56066</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19030</v>
+        <v>19031</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133374</v>
+        <v>133378</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427186</v>
+        <v>427190</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60798</v>
+        <v>60793</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3306</v>
+        <v>3311</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5561</v>
+        <v>5570</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-25 11:12:03</t>
+          <t>2026-07-26 11:20:52</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17311</v>
+        <v>16171</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81106</v>
+        <v>76924</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38440</v>
+        <v>36189</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0367</v>
+        <v>0.0345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19421</v>
+        <v>18461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0176</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174258</v>
+        <v>163127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1662</v>
+        <v>0.1556</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471244</v>
+        <v>443829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4494</v>
+        <v>0.4233</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15522</v>
+        <v>14612</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0148</v>
+        <v>0.0139</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56193</v>
+        <v>53328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0536</v>
+        <v>0.0509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2140</v>
+        <v>2026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8654</v>
+        <v>8174</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5279</v>
+        <v>5234</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6361</v>
+        <v>6283</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34173</v>
+        <v>33012</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0326</v>
+        <v>0.0315</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161692</v>
+        <v>156529</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1493</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71456</v>
+        <v>69077</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0659</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33133</v>
+        <v>32100</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.0306</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4719</v>
+        <v>4564</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18447</v>
+        <v>17860</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6804</v>
+        <v>6734</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7761</v>
+        <v>7683</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52054</v>
+        <v>52050</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52139</v>
+        <v>52146</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51918</v>
+        <v>51914</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53739</v>
+        <v>53729</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53208</v>
+        <v>53224</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53082</v>
+        <v>53050</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52900</v>
+        <v>52898</v>
       </c>
       <c r="F74" t="n">
         <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52909</v>
+        <v>52915</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52871</v>
+        <v>52873</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53090</v>
+        <v>53088</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53066</v>
+        <v>53058</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52918</v>
+        <v>52913</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52343</v>
+        <v>52345</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32063</v>
+        <v>32061</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:34</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15003</v>
+        <v>15026</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:34</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:08</t>
+          <t>2026-07-27 12:56:42</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10491</v>
+        <v>10169</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01</v>
+        <v>0.0097</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8054</v>
+        <v>7978</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:34</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:34</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5984</v>
+        <v>5985</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:55:49</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:07</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5879</v>
+        <v>5881</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5958</v>
+        <v>5961</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5941</v>
+        <v>5938</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5993</v>
+        <v>5995</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="F215" t="n">
         <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F216" t="n">
         <v>0.0012</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:41</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F226" t="n">
         <v>0.0011</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-26 11:22:06</t>
+          <t>2026-07-27 12:56:40</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17085</v>
+        <v>17080</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56066</v>
+        <v>56061</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19031</v>
+        <v>19028</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133378</v>
+        <v>133373</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427190</v>
+        <v>427185</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23553</v>
+        <v>23555</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60793</v>
+        <v>60794</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3311</v>
+        <v>3308</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4574</v>
+        <v>4573</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5570</v>
+        <v>5566</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-26 11:20:52</t>
+          <t>2026-07-27 12:56:08</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16171</v>
+        <v>17312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0154</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76924</v>
+        <v>81107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36189</v>
+        <v>38440</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0345</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18461</v>
+        <v>19424</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0176</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>163127</v>
+        <v>174259</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1556</v>
+        <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>443829</v>
+        <v>471245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4233</v>
+        <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14612</v>
+        <v>15522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0139</v>
+        <v>0.0148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53328</v>
+        <v>56198</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0509</v>
+        <v>0.0536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2026</v>
+        <v>2141</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8174</v>
+        <v>8655</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5234</v>
+        <v>5279</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6283</v>
+        <v>6362</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33012</v>
+        <v>34168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0315</v>
+        <v>0.0326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>156529</v>
+        <v>161687</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1493</v>
+        <v>0.1542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69077</v>
+        <v>71456</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0659</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32100</v>
+        <v>33141</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0306</v>
+        <v>0.0316</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4564</v>
+        <v>4714</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17860</v>
+        <v>18442</v>
       </c>
       <c r="F23" t="n">
-        <v>0.017</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6734</v>
+        <v>6819</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7683</v>
+        <v>7752</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0073</v>
+        <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51969</v>
+        <v>51977</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51968</v>
+        <v>51976</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52956</v>
+        <v>52954</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52923</v>
+        <v>52915</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53234</v>
+        <v>53229</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52050</v>
+        <v>52054</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54521</v>
+        <v>54519</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52146</v>
+        <v>52144</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53026</v>
+        <v>53024</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53102</v>
+        <v>53098</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51914</v>
+        <v>51908</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54591</v>
+        <v>54604</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53729</v>
+        <v>53739</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53224</v>
+        <v>53221</v>
       </c>
       <c r="F71" t="n">
         <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53050</v>
+        <v>53082</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52917</v>
+        <v>52914</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52898</v>
+        <v>52902</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52838</v>
+        <v>52844</v>
       </c>
       <c r="F75" t="n">
         <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52821</v>
+        <v>52820</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52891</v>
+        <v>52892</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52915</v>
+        <v>52913</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52892</v>
+        <v>52898</v>
       </c>
       <c r="F80" t="n">
         <v>0.0504</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52873</v>
+        <v>52866</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53088</v>
+        <v>53086</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53058</v>
+        <v>53056</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52984</v>
+        <v>52988</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52913</v>
+        <v>52908</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52847</v>
+        <v>52845</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53157</v>
+        <v>53172</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52345</v>
+        <v>52338</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32061</v>
+        <v>32062</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:58:34</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15026</v>
+        <v>15004</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:58:34</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:42</t>
+          <t>2026-07-28 11:59:16</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10169</v>
+        <v>10491</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7978</v>
+        <v>8055</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:58:34</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:58:34</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F102" t="n">
         <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5985</v>
+        <v>5987</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="F165" t="n">
         <v>0.0057</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-27 12:55:49</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6151,14 +6151,14 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="F174" t="n">
         <v>0.0012</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6075</v>
+        <v>6077</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5961</v>
+        <v>5958</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="F196" t="n">
         <v>0.0012</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5996</v>
+        <v>5994</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6028</v>
+        <v>6030</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F216" t="n">
         <v>0.0012</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:41</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:15</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F226" t="n">
         <v>0.0011</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:40</t>
+          <t>2026-07-28 11:59:14</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17080</v>
+        <v>17079</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:55</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56061</v>
+        <v>56060</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:55</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:55</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19028</v>
+        <v>19032</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:55</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133373</v>
+        <v>133372</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427185</v>
+        <v>427184</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23555</v>
+        <v>23557</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60794</v>
+        <v>60797</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5566</v>
+        <v>5569</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-27 12:56:08</t>
+          <t>2026-07-28 11:58:56</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17312</v>
+        <v>14002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0134</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81107</v>
+        <v>68810</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38440</v>
+        <v>32137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0367</v>
+        <v>0.0306</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19424</v>
+        <v>16989</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174259</v>
+        <v>145727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1662</v>
+        <v>0.139</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471245</v>
+        <v>393309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4494</v>
+        <v>0.3751</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15522</v>
+        <v>14033</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0148</v>
+        <v>0.0134</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56198</v>
+        <v>47635</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0536</v>
+        <v>0.0454</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2141</v>
+        <v>1798</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0017</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8655</v>
+        <v>7214</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0069</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5279</v>
+        <v>5164</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6362</v>
+        <v>6158</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.0059</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:40</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34168</v>
+        <v>30815</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0326</v>
+        <v>0.0294</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161687</v>
+        <v>146467</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>0.1397</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71456</v>
+        <v>64776</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0618</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33141</v>
+        <v>30696</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0316</v>
+        <v>0.0293</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4714</v>
+        <v>4272</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0041</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18442</v>
+        <v>16704</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.0159</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6819</v>
+        <v>6669</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7752</v>
+        <v>7550</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0074</v>
+        <v>0.0072</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51977</v>
+        <v>51964</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51976</v>
+        <v>51957</v>
       </c>
       <c r="F27" t="n">
         <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52954</v>
+        <v>52950</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52915</v>
+        <v>52914</v>
       </c>
       <c r="F55" t="n">
         <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53229</v>
+        <v>53245</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52054</v>
+        <v>52032</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52144</v>
+        <v>52142</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53098</v>
+        <v>53100</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51908</v>
+        <v>51888</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53739</v>
+        <v>53733</v>
       </c>
       <c r="F70" t="n">
         <v>0.0512</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53221</v>
+        <v>53197</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53082</v>
+        <v>53084</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52820</v>
+        <v>52817</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52660</v>
+        <v>52665</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52913</v>
+        <v>52902</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52866</v>
+        <v>52870</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53056</v>
+        <v>53064</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52988</v>
+        <v>52992</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52908</v>
+        <v>52907</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52845</v>
+        <v>52851</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53172</v>
+        <v>53164</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52338</v>
+        <v>52341</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32062</v>
+        <v>32061</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:34</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15004</v>
+        <v>15012</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:34</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8843</v>
+        <v>8842</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:16</t>
+          <t>2026-07-29 12:03:42</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10491</v>
+        <v>9517</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01</v>
+        <v>0.0091</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8055</v>
+        <v>7811</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0077</v>
+        <v>0.0074</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:34</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:34</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5874</v>
+        <v>5873</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5880</v>
+        <v>5878</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5725</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5812</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>5799</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5974</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5987</v>
+        <v>5984</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:01:57</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6151,14 +6151,14 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="F174" t="n">
         <v>0.0012</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5866</v>
+        <v>5865</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5881</v>
+        <v>5879</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5920</v>
+        <v>5918</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5829</v>
+        <v>5828</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F196" t="n">
         <v>0.0012</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5976</v>
+        <v>5974</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5997</v>
+        <v>5995</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6016</v>
+        <v>6014</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6030</v>
+        <v>6027</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:15</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F226" t="n">
         <v>0.0011</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5836</v>
+        <v>5835</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-28 11:59:14</t>
+          <t>2026-07-29 12:03:41</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17079</v>
+        <v>17084</v>
       </c>
       <c r="F230" t="n">
         <v>0.0163</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:55</t>
+          <t>2026-07-29 12:02:15</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56060</v>
+        <v>56065</v>
       </c>
       <c r="F231" t="n">
         <v>0.0535</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:55</t>
+          <t>2026-07-29 12:02:15</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:55</t>
+          <t>2026-07-29 12:02:15</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19032</v>
+        <v>19035</v>
       </c>
       <c r="F233" t="n">
         <v>0.0182</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:55</t>
+          <t>2026-07-29 12:02:15</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133372</v>
+        <v>133377</v>
       </c>
       <c r="F234" t="n">
         <v>0.1272</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:15</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427184</v>
+        <v>427189</v>
       </c>
       <c r="F235" t="n">
         <v>0.4074</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23557</v>
+        <v>23545</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60797</v>
+        <v>60803</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3307</v>
+        <v>3311</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5569</v>
+        <v>5572</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-28 11:58:56</t>
+          <t>2026-07-29 12:02:16</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14002</v>
+        <v>16752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0134</v>
+        <v>0.016</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>68810</v>
+        <v>76857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0733</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32137</v>
+        <v>36652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0306</v>
+        <v>0.035</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16989</v>
+        <v>18845</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0162</v>
+        <v>0.018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>145727</v>
+        <v>164673</v>
       </c>
       <c r="F6" t="n">
-        <v>0.139</v>
+        <v>0.157</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>393309</v>
+        <v>447031</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3751</v>
+        <v>0.4263</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14033</v>
+        <v>15061</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0134</v>
+        <v>0.0144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47635</v>
+        <v>53813</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0454</v>
+        <v>0.0513</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1798</v>
+        <v>2033</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0017</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7214</v>
+        <v>8181</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0069</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5164</v>
+        <v>5244</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6158</v>
+        <v>6297</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:40</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30815</v>
+        <v>33597</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0294</v>
+        <v>0.032</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:58</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>146467</v>
+        <v>156466</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1397</v>
+        <v>0.1492</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>64776</v>
+        <v>69535</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0618</v>
+        <v>0.0663</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30696</v>
+        <v>32540</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0293</v>
+        <v>0.031</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4272</v>
+        <v>4575</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0041</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16704</v>
+        <v>17871</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0159</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6669</v>
+        <v>6763</v>
       </c>
       <c r="F24" t="n">
         <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7550</v>
+        <v>7699</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51964</v>
+        <v>51960</v>
       </c>
       <c r="F26" t="n">
         <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>48540</v>
+        <v>49340</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0463</v>
+        <v>0.0471</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>48619</v>
+        <v>49429</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0464</v>
+        <v>0.0471</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49326</v>
+        <v>50136</v>
       </c>
       <c r="F33" t="n">
-        <v>0.047</v>
+        <v>0.0478</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1729,14 +1729,14 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>49358</v>
+        <v>50175</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0471</v>
+        <v>0.0479</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>49407</v>
+        <v>50261</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0471</v>
+        <v>0.0479</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>49832</v>
+        <v>50622</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0475</v>
+        <v>0.0483</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>51706</v>
+        <v>52540</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0493</v>
+        <v>0.0501</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51630</v>
+        <v>52461</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0492</v>
+        <v>0.05</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51688</v>
+        <v>52528</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0493</v>
+        <v>0.0501</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52950</v>
+        <v>52955</v>
       </c>
       <c r="F54" t="n">
         <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50645</v>
+        <v>51494</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0483</v>
+        <v>0.0491</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2389,14 +2389,14 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>50989</v>
+        <v>51836</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0486</v>
+        <v>0.0494</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>50907</v>
+        <v>51755</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0485</v>
+        <v>0.0494</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53245</v>
+        <v>53242</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52032</v>
+        <v>52050</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54519</v>
+        <v>54530</v>
       </c>
       <c r="F64" t="n">
         <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53024</v>
+        <v>53006</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53100</v>
+        <v>53099</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51888</v>
+        <v>51908</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54604</v>
+        <v>54586</v>
       </c>
       <c r="F69" t="n">
         <v>0.0521</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53197</v>
+        <v>53214</v>
       </c>
       <c r="F71" t="n">
         <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52914</v>
+        <v>52906</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52817</v>
+        <v>52821</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52892</v>
+        <v>52895</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52665</v>
+        <v>52663</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52902</v>
+        <v>52907</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52898</v>
+        <v>52905</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52870</v>
+        <v>52866</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53086</v>
+        <v>53088</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53064</v>
+        <v>53054</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52992</v>
+        <v>52984</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52907</v>
+        <v>52915</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52851</v>
+        <v>52849</v>
       </c>
       <c r="F86" t="n">
         <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53164</v>
+        <v>53162</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52341</v>
+        <v>52344</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54027</v>
+        <v>54029</v>
       </c>
       <c r="F89" t="n">
         <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32061</v>
+        <v>32063</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15012</v>
+        <v>15022</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8842</v>
+        <v>8839</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:42</t>
+          <t>2026-07-30 11:54:00</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>9517</v>
+        <v>10143</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0091</v>
+        <v>0.0097</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7811</v>
+        <v>7972</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0074</v>
+        <v>0.0076</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4039,14 +4039,14 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>954</v>
+        <v>971</v>
       </c>
       <c r="F110" t="n">
         <v>0.0009</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5725</v>
+        <v>5739</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -4171,14 +4171,14 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="F114" t="n">
         <v>0.0009</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5731</v>
+        <v>5745</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4237,14 +4237,14 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="F116" t="n">
         <v>0.0009</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5764</v>
+        <v>5779</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4699,14 +4699,14 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="F130" t="n">
         <v>0.0009</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5761</v>
+        <v>5775</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:52:47</t>
         </is>
       </c>
     </row>
@@ -4831,14 +4831,14 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="F134" t="n">
         <v>0.0009</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5751</v>
+        <v>5762</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5161,14 +5161,14 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1012</v>
+        <v>1029</v>
       </c>
       <c r="F144" t="n">
         <v>0.001</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5799</v>
+        <v>5814</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5293,14 +5293,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="F148" t="n">
         <v>0.0012</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5911</v>
+        <v>5924</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5359,14 +5359,14 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="F150" t="n">
         <v>0.0012</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5895</v>
+        <v>5911</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5425,14 +5425,14 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="F152" t="n">
         <v>0.0012</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5917</v>
+        <v>5933</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5974</v>
+        <v>5976</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5984</v>
+        <v>5986</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1170</v>
+        <v>1189</v>
       </c>
       <c r="F168" t="n">
         <v>0.0011</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5919</v>
+        <v>5935</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-29 12:01:57</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1185</v>
+        <v>1205</v>
       </c>
       <c r="F170" t="n">
         <v>0.0011</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5940</v>
+        <v>5963</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6085,14 +6085,14 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="F172" t="n">
         <v>0.0011</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5917</v>
+        <v>5935</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="F175" t="n">
         <v>0.0057</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F176" t="n">
         <v>0.0011</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5915</v>
+        <v>5920</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F195" t="n">
         <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5995</v>
+        <v>5997</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6014</v>
+        <v>6016</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6002</v>
+        <v>6004</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-29 12:03:41</t>
+          <t>2026-07-30 11:53:59</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:15</t>
+          <t>2026-07-30 11:53:05</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:15</t>
+          <t>2026-07-30 11:53:05</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:15</t>
+          <t>2026-07-30 11:53:05</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19035</v>
+        <v>19032</v>
       </c>
       <c r="F233" t="n">
         <v>0.0182</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:15</t>
+          <t>2026-07-30 11:53:05</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:15</t>
+          <t>2026-07-30 11:53:05</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23545</v>
+        <v>23553</v>
       </c>
       <c r="F236" t="n">
         <v>0.0225</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60803</v>
+        <v>60813</v>
       </c>
       <c r="F237" t="n">
         <v>0.058</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="F243" t="n">
         <v>0.0032</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4573</v>
+        <v>4574</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5572</v>
+        <v>5570</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-29 12:02:16</t>
+          <t>2026-07-30 11:53:06</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16752</v>
+        <v>15059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.016</v>
+        <v>0.0144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:23</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76857</v>
+        <v>73098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0733</v>
+        <v>0.0697</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:23</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36652</v>
+        <v>34013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.035</v>
+        <v>0.0324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:23</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18845</v>
+        <v>17405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.018</v>
+        <v>0.0166</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:23</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>164673</v>
+        <v>152947</v>
       </c>
       <c r="F6" t="n">
-        <v>0.157</v>
+        <v>0.1459</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:23</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>447031</v>
+        <v>418467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4263</v>
+        <v>0.3991</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15061</v>
+        <v>13828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0144</v>
+        <v>0.0132</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53813</v>
+        <v>50499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0513</v>
+        <v>0.0482</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2033</v>
+        <v>1920</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8181</v>
+        <v>7702</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0073</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5244</v>
+        <v>5158</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6297</v>
+        <v>6210</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0059</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33597</v>
+        <v>31715</v>
       </c>
       <c r="F18" t="n">
-        <v>0.032</v>
+        <v>0.0302</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:58</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>156466</v>
+        <v>151638</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1492</v>
+        <v>0.1446</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69535</v>
+        <v>66643</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0663</v>
+        <v>0.0636</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32540</v>
+        <v>31003</v>
       </c>
       <c r="F21" t="n">
-        <v>0.031</v>
+        <v>0.0296</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4575</v>
+        <v>4468</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0043</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17871</v>
+        <v>17332</v>
       </c>
       <c r="F23" t="n">
-        <v>0.017</v>
+        <v>0.0165</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6763</v>
+        <v>6694</v>
       </c>
       <c r="F24" t="n">
         <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7699</v>
+        <v>7622</v>
       </c>
       <c r="F25" t="n">
         <v>0.0073</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51960</v>
+        <v>51173</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0496</v>
+        <v>0.0488</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51957</v>
+        <v>51157</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0496</v>
+        <v>0.0488</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1333,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>52174</v>
+        <v>51335</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0498</v>
+        <v>0.049</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50988</v>
+        <v>50141</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0486</v>
+        <v>0.0478</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>48332</v>
+        <v>49133</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0461</v>
+        <v>0.0469</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>51009</v>
+        <v>50162</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0486</v>
+        <v>0.0478</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1663,14 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>50939</v>
+        <v>51770</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0486</v>
+        <v>0.0494</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>43377</v>
+        <v>44199</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0414</v>
+        <v>0.0422</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>49416</v>
+        <v>50252</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0471</v>
+        <v>0.0479</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>52195</v>
+        <v>51356</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0498</v>
+        <v>0.049</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52955</v>
+        <v>52104</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0505</v>
+        <v>0.0497</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52914</v>
+        <v>52065</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0505</v>
+        <v>0.0497</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53242</v>
+        <v>53233</v>
       </c>
       <c r="F62" t="n">
         <v>0.0508</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52050</v>
+        <v>51228</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0496</v>
+        <v>0.0489</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>54530</v>
+        <v>53657</v>
       </c>
       <c r="F64" t="n">
-        <v>0.052</v>
+        <v>0.0512</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52142</v>
+        <v>51323</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0497</v>
+        <v>0.0489</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53006</v>
+        <v>53026</v>
       </c>
       <c r="F66" t="n">
         <v>0.0506</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53099</v>
+        <v>53100</v>
       </c>
       <c r="F67" t="n">
         <v>0.0506</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51908</v>
+        <v>51096</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0495</v>
+        <v>0.0487</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54586</v>
+        <v>53736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0521</v>
+        <v>0.0512</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53733</v>
+        <v>52873</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0512</v>
+        <v>0.0504</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53214</v>
+        <v>52373</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0507</v>
+        <v>0.0499</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53084</v>
+        <v>52232</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0506</v>
+        <v>0.0498</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52906</v>
+        <v>52911</v>
       </c>
       <c r="F73" t="n">
         <v>0.0505</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52902</v>
+        <v>52044</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0505</v>
+        <v>0.0496</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52844</v>
+        <v>51982</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0504</v>
+        <v>0.0496</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52821</v>
+        <v>51967</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0504</v>
+        <v>0.0496</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:25</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52895</v>
+        <v>52889</v>
       </c>
       <c r="F77" t="n">
         <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52663</v>
+        <v>52660</v>
       </c>
       <c r="F78" t="n">
         <v>0.0502</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52907</v>
+        <v>52076</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0505</v>
+        <v>0.0497</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52905</v>
+        <v>52045</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0505</v>
+        <v>0.0496</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52866</v>
+        <v>52007</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0504</v>
+        <v>0.0496</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53088</v>
+        <v>52224</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0506</v>
+        <v>0.0498</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53054</v>
+        <v>52206</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0506</v>
+        <v>0.0498</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52984</v>
+        <v>52991</v>
       </c>
       <c r="F84" t="n">
         <v>0.0505</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52915</v>
+        <v>52056</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0505</v>
+        <v>0.0496</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>52849</v>
+        <v>51990</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0504</v>
+        <v>0.0496</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53162</v>
+        <v>53168</v>
       </c>
       <c r="F87" t="n">
         <v>0.0507</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52344</v>
+        <v>51501</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0499</v>
+        <v>0.0491</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>54029</v>
+        <v>53163</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0515</v>
+        <v>0.0507</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32063</v>
+        <v>32055</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15022</v>
+        <v>14964</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8839</v>
+        <v>8853</v>
       </c>
       <c r="F97" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:00</t>
+          <t>2026-07-31 12:03:26</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10143</v>
+        <v>9865</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0097</v>
+        <v>0.0094</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7972</v>
+        <v>7878</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1105</v>
+        <v>1088</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5873</v>
+        <v>5858</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3841,14 +3841,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>1090</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5879</v>
+        <v>5864</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3907,14 +3907,14 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="F106" t="n">
         <v>0.0012</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5819</v>
+        <v>5803</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3973,14 +3973,14 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1135</v>
+        <v>1115</v>
       </c>
       <c r="F108" t="n">
         <v>0.0011</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5813</v>
+        <v>5794</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5739</v>
+        <v>5738</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4105,14 +4105,14 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="F112" t="n">
         <v>0.0009</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5736</v>
+        <v>5749</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5745</v>
+        <v>5744</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5779</v>
+        <v>5778</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5661</v>
+        <v>5660</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4369,14 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1135</v>
+        <v>1115</v>
       </c>
       <c r="F120" t="n">
         <v>0.0011</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5813</v>
+        <v>5794</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -4567,14 +4567,14 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>991</v>
+        <v>1008</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5805</v>
+        <v>5820</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4633,14 +4633,14 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1008</v>
+        <v>1028</v>
       </c>
       <c r="F128" t="n">
         <v>0.001</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5810</v>
+        <v>5826</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4765,14 +4765,14 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>952</v>
+        <v>968</v>
       </c>
       <c r="F132" t="n">
         <v>0.0009</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5748</v>
+        <v>5759</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:47</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5778</v>
+        <v>5777</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5814</v>
+        <v>5813</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5924</v>
+        <v>5923</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5933</v>
+        <v>5932</v>
       </c>
       <c r="F153" t="n">
         <v>0.0057</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5557,14 +5557,14 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="F156" t="n">
         <v>0.0012</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5819</v>
+        <v>5803</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5623,14 +5623,14 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1237</v>
+        <v>1217</v>
       </c>
       <c r="F158" t="n">
         <v>0.0012</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5976</v>
+        <v>5952</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1237</v>
+        <v>1217</v>
       </c>
       <c r="F160" t="n">
         <v>0.0012</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5986</v>
+        <v>5963</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:00:56</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5935</v>
+        <v>5934</v>
       </c>
       <c r="F169" t="n">
         <v>0.0057</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5935</v>
+        <v>5934</v>
       </c>
       <c r="F173" t="n">
         <v>0.0057</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5865</v>
+        <v>5850</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1464</v>
+        <v>1441</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6067</v>
+        <v>6048</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1142</v>
+        <v>1124</v>
       </c>
       <c r="F180" t="n">
         <v>0.0011</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5880</v>
+        <v>5863</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1080</v>
+        <v>1064</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5829</v>
+        <v>5815</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1471</v>
+        <v>1447</v>
       </c>
       <c r="F188" t="n">
         <v>0.0014</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6076</v>
+        <v>6059</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1347</v>
+        <v>1324</v>
       </c>
       <c r="F190" t="n">
         <v>0.0013</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5920</v>
+        <v>5907</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1287</v>
+        <v>1262</v>
       </c>
       <c r="F192" t="n">
         <v>0.0012</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5959</v>
+        <v>5942</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1266</v>
+        <v>1245</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5941</v>
+        <v>5917</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5997</v>
+        <v>5995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1240</v>
+        <v>1219</v>
       </c>
       <c r="F198" t="n">
         <v>0.0012</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5995</v>
+        <v>5973</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1234</v>
+        <v>1214</v>
       </c>
       <c r="F200" t="n">
         <v>0.0012</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5996</v>
+        <v>5977</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="F202" t="n">
         <v>0.0012</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5977</v>
+        <v>5953</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6016</v>
+        <v>5997</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1238</v>
+        <v>1218</v>
       </c>
       <c r="F210" t="n">
         <v>0.0012</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6017</v>
+        <v>5992</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="F212" t="n">
         <v>0.0012</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6010</v>
+        <v>5990</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1253</v>
+        <v>1232</v>
       </c>
       <c r="F214" t="n">
         <v>0.0012</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6031</v>
+        <v>6010</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1250</v>
+        <v>1229</v>
       </c>
       <c r="F216" t="n">
         <v>0.0012</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6019</v>
+        <v>6004</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1237</v>
+        <v>1216</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6019</v>
+        <v>5995</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1232</v>
+        <v>1212</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6004</v>
+        <v>5980</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="F226" t="n">
         <v>0.0011</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5836</v>
+        <v>5820</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1386</v>
+        <v>1363</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:59</t>
+          <t>2026-07-31 12:03:24</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>17084</v>
+        <v>16911</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0163</v>
+        <v>0.0161</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:05</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>56065</v>
+        <v>55972</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0535</v>
+        <v>0.0534</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:05</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>31025</v>
+        <v>30898</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0296</v>
+        <v>0.0295</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:05</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>19032</v>
+        <v>18955</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:05</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>133377</v>
+        <v>131834</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1272</v>
+        <v>0.1257</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:05</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>427189</v>
+        <v>422204</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4074</v>
+        <v>0.4026</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23553</v>
+        <v>23411</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0225</v>
+        <v>0.0223</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60813</v>
+        <v>60147</v>
       </c>
       <c r="F237" t="n">
-        <v>0.058</v>
+        <v>0.0574</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3310</v>
+        <v>3298</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4574</v>
+        <v>4592</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5570</v>
+        <v>5568</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:06</t>
+          <t>2026-07-31 12:01:14</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15059</v>
+        <v>17177</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0144</v>
+        <v>0.0164</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:23</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73098</v>
+        <v>81044</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0697</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:23</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34013</v>
+        <v>38299</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0324</v>
+        <v>0.0365</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:23</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17405</v>
+        <v>19373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0166</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:23</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>152947</v>
+        <v>172850</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1459</v>
+        <v>0.1648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:23</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>418467</v>
+        <v>467350</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3991</v>
+        <v>0.4457</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13828</v>
+        <v>15836</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0132</v>
+        <v>0.0151</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50499</v>
+        <v>55785</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0482</v>
+        <v>0.0532</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1920</v>
+        <v>2148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0018</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7702</v>
+        <v>8662</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0073</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5158</v>
+        <v>5321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0049</v>
+        <v>0.0051</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6210</v>
+        <v>6388</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0059</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>31715</v>
+        <v>33801</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0302</v>
+        <v>0.0322</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>151638</v>
+        <v>161496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1446</v>
+        <v>0.154</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>66643</v>
+        <v>71181</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0636</v>
+        <v>0.0679</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31003</v>
+        <v>32958</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0296</v>
+        <v>0.0314</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4468</v>
+        <v>4773</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0043</v>
+        <v>0.0046</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17332</v>
+        <v>18501</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0165</v>
+        <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6694</v>
+        <v>6853</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7622</v>
+        <v>7796</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0073</v>
+        <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51173</v>
+        <v>51165</v>
       </c>
       <c r="F26" t="n">
         <v>0.0488</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51157</v>
+        <v>51155</v>
       </c>
       <c r="F27" t="n">
         <v>0.0488</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49340</v>
+        <v>48545</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0471</v>
+        <v>0.0463</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49133</v>
+        <v>48349</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0469</v>
+        <v>0.0461</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>49429</v>
+        <v>48648</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0471</v>
+        <v>0.0464</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50136</v>
+        <v>49314</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0478</v>
+        <v>0.047</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48442</v>
+        <v>48415</v>
       </c>
       <c r="F34" t="n">
         <v>0.0462</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1597,14 +1597,14 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>51210</v>
+        <v>50373</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0488</v>
+        <v>0.048</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>51073</v>
+        <v>50243</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0487</v>
+        <v>0.0479</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1663,14 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>51770</v>
+        <v>50942</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0494</v>
+        <v>0.0486</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>44199</v>
+        <v>43351</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0422</v>
+        <v>0.0413</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1729,14 +1729,14 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>50175</v>
+        <v>49372</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0479</v>
+        <v>0.0471</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>50252</v>
+        <v>49438</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0479</v>
+        <v>0.0471</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>50261</v>
+        <v>49451</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0479</v>
+        <v>0.0472</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>50526</v>
+        <v>49704</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0482</v>
+        <v>0.0474</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>42902</v>
+        <v>42054</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0409</v>
+        <v>0.0401</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>50671</v>
+        <v>49860</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0483</v>
+        <v>0.0476</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>42878</v>
+        <v>42042</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0409</v>
+        <v>0.0401</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>50622</v>
+        <v>49806</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0483</v>
+        <v>0.0475</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>52244</v>
+        <v>51407</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0498</v>
+        <v>0.049</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>52540</v>
+        <v>51696</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0501</v>
+        <v>0.0493</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>52461</v>
+        <v>51611</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05</v>
+        <v>0.0492</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>52528</v>
+        <v>51686</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0501</v>
+        <v>0.0493</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>50618</v>
+        <v>50609</v>
       </c>
       <c r="F52" t="n">
         <v>0.0483</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52104</v>
+        <v>52099</v>
       </c>
       <c r="F54" t="n">
         <v>0.0497</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52065</v>
+        <v>52068</v>
       </c>
       <c r="F55" t="n">
         <v>0.0497</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2257,14 +2257,14 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>51219</v>
+        <v>50361</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0488</v>
+        <v>0.048</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>51073</v>
+        <v>50230</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0487</v>
+        <v>0.0479</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2323,14 +2323,14 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>52043</v>
+        <v>51193</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0496</v>
+        <v>0.0488</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>51494</v>
+        <v>50654</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0491</v>
+        <v>0.0483</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -2389,14 +2389,14 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>51836</v>
+        <v>50990</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0494</v>
+        <v>0.0486</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>51755</v>
+        <v>50908</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0494</v>
+        <v>0.0485</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2455,14 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53233</v>
+        <v>52396</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0508</v>
+        <v>0.05</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>51228</v>
+        <v>52056</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0489</v>
+        <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53657</v>
+        <v>53645</v>
       </c>
       <c r="F64" t="n">
         <v>0.0512</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>51323</v>
+        <v>51322</v>
       </c>
       <c r="F65" t="n">
         <v>0.0489</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53026</v>
+        <v>52176</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0506</v>
+        <v>0.0498</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53100</v>
+        <v>52219</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0506</v>
+        <v>0.0498</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51096</v>
+        <v>51119</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0487</v>
+        <v>0.0488</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53736</v>
+        <v>53737</v>
       </c>
       <c r="F69" t="n">
         <v>0.0512</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>52873</v>
+        <v>52883</v>
       </c>
       <c r="F70" t="n">
         <v>0.0504</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>52373</v>
+        <v>52381</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0499</v>
+        <v>0.05</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>52232</v>
+        <v>52214</v>
       </c>
       <c r="F72" t="n">
         <v>0.0498</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52911</v>
+        <v>52058</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0505</v>
+        <v>0.0496</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52044</v>
+        <v>52886</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>51982</v>
+        <v>51963</v>
       </c>
       <c r="F75" t="n">
         <v>0.0496</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>51967</v>
+        <v>51963</v>
       </c>
       <c r="F76" t="n">
         <v>0.0496</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:25</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52889</v>
+        <v>52030</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0504</v>
+        <v>0.0496</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52660</v>
+        <v>51808</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0502</v>
+        <v>0.0494</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52076</v>
+        <v>52074</v>
       </c>
       <c r="F79" t="n">
         <v>0.0497</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>52045</v>
+        <v>52046</v>
       </c>
       <c r="F80" t="n">
         <v>0.0496</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52007</v>
+        <v>52005</v>
       </c>
       <c r="F81" t="n">
         <v>0.0496</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>52224</v>
+        <v>52223</v>
       </c>
       <c r="F82" t="n">
         <v>0.0498</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>52206</v>
+        <v>52204</v>
       </c>
       <c r="F83" t="n">
         <v>0.0498</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52991</v>
+        <v>52141</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0505</v>
+        <v>0.0497</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52056</v>
+        <v>52062</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>51990</v>
+        <v>51995</v>
       </c>
       <c r="F86" t="n">
         <v>0.0496</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53168</v>
+        <v>52287</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0507</v>
+        <v>0.0499</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>51501</v>
+        <v>51521</v>
       </c>
       <c r="F88" t="n">
         <v>0.0491</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53163</v>
+        <v>53160</v>
       </c>
       <c r="F89" t="n">
         <v>0.0507</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32055</v>
+        <v>32060</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>14964</v>
+        <v>14988</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8853</v>
+        <v>8867</v>
       </c>
       <c r="F97" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:26</t>
+          <t>2026-08-01 11:18:30</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>9865</v>
+        <v>10491</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0094</v>
+        <v>0.01</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7878</v>
+        <v>8071</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0075</v>
+        <v>0.0077</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4039,14 +4039,14 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="F110" t="n">
         <v>0.0009</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5738</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4105,14 +4105,14 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="F112" t="n">
         <v>0.0009</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5749</v>
+        <v>5734</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4171,14 +4171,14 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="F114" t="n">
         <v>0.0009</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5744</v>
+        <v>5726</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4237,14 +4237,14 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="F116" t="n">
         <v>0.0009</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5778</v>
+        <v>5762</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5660</v>
+        <v>5662</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4435,14 +4435,14 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1235</v>
+        <v>1215</v>
       </c>
       <c r="F122" t="n">
         <v>0.0012</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5946</v>
+        <v>5931</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1233</v>
+        <v>1213</v>
       </c>
       <c r="F124" t="n">
         <v>0.0012</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5923</v>
+        <v>5904</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4567,14 +4567,14 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="F126" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5820</v>
+        <v>5806</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4633,14 +4633,14 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="F128" t="n">
         <v>0.001</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5826</v>
+        <v>5808</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4699,14 +4699,14 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="F130" t="n">
         <v>0.0009</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5774</v>
+        <v>5764</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4765,14 +4765,14 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="F132" t="n">
         <v>0.0009</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5759</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4831,14 +4831,14 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="F134" t="n">
         <v>0.0009</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5761</v>
+        <v>5750</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4897,14 +4897,14 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="F136" t="n">
         <v>0.0009</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5786</v>
+        <v>5775</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4963,14 +4963,14 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>994</v>
+        <v>973</v>
       </c>
       <c r="F138" t="n">
         <v>0.0009</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5774</v>
+        <v>5754</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5029,14 +5029,14 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="F140" t="n">
         <v>0.0009</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5777</v>
+        <v>5765</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5095,14 +5095,14 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="F142" t="n">
         <v>0.0009</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5774</v>
+        <v>5751</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5161,14 +5161,14 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1029</v>
+        <v>1012</v>
       </c>
       <c r="F144" t="n">
         <v>0.001</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5813</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5227,14 +5227,14 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1214</v>
+        <v>1194</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5883</v>
+        <v>5864</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5293,14 +5293,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1274</v>
+        <v>1253</v>
       </c>
       <c r="F148" t="n">
         <v>0.0012</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5923</v>
+        <v>5912</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5359,14 +5359,14 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1274</v>
+        <v>1253</v>
       </c>
       <c r="F150" t="n">
         <v>0.0012</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5910</v>
+        <v>5894</v>
       </c>
       <c r="F151" t="n">
         <v>0.0056</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5425,14 +5425,14 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1274</v>
+        <v>1253</v>
       </c>
       <c r="F152" t="n">
         <v>0.0012</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5932</v>
+        <v>5916</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5491,14 +5491,14 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F154" t="n">
         <v>0.001</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5690</v>
+        <v>5686</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -5623,14 +5623,14 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F158" t="n">
         <v>0.0012</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5952</v>
+        <v>5951</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5755,14 +5755,14 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>1181</v>
       </c>
       <c r="F162" t="n">
         <v>0.0011</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5962</v>
+        <v>5941</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1189</v>
+        <v>1170</v>
       </c>
       <c r="F164" t="n">
         <v>0.0011</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5930</v>
+        <v>5914</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:56</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5887,14 +5887,14 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1217</v>
+        <v>1197</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5956</v>
+        <v>5938</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1189</v>
+        <v>1169</v>
       </c>
       <c r="F168" t="n">
         <v>0.0011</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5934</v>
+        <v>5917</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1205</v>
+        <v>1185</v>
       </c>
       <c r="F170" t="n">
         <v>0.0011</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5962</v>
+        <v>5939</v>
       </c>
       <c r="F171" t="n">
         <v>0.0057</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -6085,14 +6085,14 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="F172" t="n">
         <v>0.0011</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5934</v>
+        <v>5916</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:29</t>
         </is>
       </c>
     </row>
@@ -6151,14 +6151,14 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1307</v>
+        <v>1285</v>
       </c>
       <c r="F174" t="n">
         <v>0.0012</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5935</v>
+        <v>5921</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1089</v>
+        <v>1107</v>
       </c>
       <c r="F176" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5850</v>
+        <v>5865</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6048</v>
+        <v>6047</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5863</v>
+        <v>5861</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1233</v>
+        <v>1213</v>
       </c>
       <c r="F182" t="n">
         <v>0.0012</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5897</v>
+        <v>5879</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1271</v>
+        <v>1249</v>
       </c>
       <c r="F184" t="n">
         <v>0.0012</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5918</v>
+        <v>5902</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6059</v>
+        <v>6055</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F192" t="n">
         <v>0.0012</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F195" t="n">
         <v>0.0056</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1242</v>
+        <v>1220</v>
       </c>
       <c r="F196" t="n">
         <v>0.0012</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5995</v>
+        <v>5975</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1219</v>
+        <v>1241</v>
       </c>
       <c r="F198" t="n">
         <v>0.0012</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5973</v>
+        <v>5992</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F200" t="n">
         <v>0.0012</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1238</v>
+        <v>1217</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6007</v>
+        <v>5986</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="F206" t="n">
         <v>0.0012</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5995</v>
+        <v>5976</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5997</v>
+        <v>5995</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="F214" t="n">
         <v>0.0012</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6010</v>
+        <v>6007</v>
       </c>
       <c r="F215" t="n">
         <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1251</v>
+        <v>1230</v>
       </c>
       <c r="F218" t="n">
         <v>0.0012</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6015</v>
+        <v>5994</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1266</v>
+        <v>1240</v>
       </c>
       <c r="F224" t="n">
         <v>0.0012</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5915</v>
+        <v>5901</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-31 12:03:24</t>
+          <t>2026-08-01 11:18:28</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>16911</v>
+        <v>16847</v>
       </c>
       <c r="F230" t="n">
         <v>0.0161</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:44</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>55972</v>
+        <v>55932</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0534</v>
+        <v>0.0533</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:44</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>30898</v>
+        <v>30889</v>
       </c>
       <c r="F232" t="n">
         <v>0.0295</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:44</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>18955</v>
+        <v>18940</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:44</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>131834</v>
+        <v>131352</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1257</v>
+        <v>0.1253</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:44</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>422204</v>
+        <v>420691</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4026</v>
+        <v>0.4012</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23411</v>
+        <v>23329</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0223</v>
+        <v>0.0222</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>60147</v>
+        <v>59976</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0574</v>
+        <v>0.0572</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3298</v>
+        <v>3292</v>
       </c>
       <c r="F243" t="n">
         <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4592</v>
+        <v>4577</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5568</v>
+        <v>5560</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-31 12:01:14</t>
+          <t>2026-08-01 11:17:45</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:07</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:07</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:07</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:07</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:07</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33801</v>
+        <v>33796</v>
       </c>
       <c r="F18" t="n">
         <v>0.0322</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161496</v>
+        <v>161491</v>
       </c>
       <c r="F19" t="n">
         <v>0.154</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32958</v>
+        <v>32957</v>
       </c>
       <c r="F21" t="n">
         <v>0.0314</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4773</v>
+        <v>4768</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0046</v>
+        <v>0.0045</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18501</v>
+        <v>18496</v>
       </c>
       <c r="F23" t="n">
         <v>0.0176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6853</v>
+        <v>6850</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7796</v>
+        <v>7797</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51119</v>
+        <v>51115</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0488</v>
+        <v>0.0487</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>52883</v>
+        <v>52875</v>
       </c>
       <c r="F70" t="n">
         <v>0.0504</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52074</v>
+        <v>52078</v>
       </c>
       <c r="F79" t="n">
         <v>0.0497</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52005</v>
+        <v>52006</v>
       </c>
       <c r="F81" t="n">
         <v>0.0496</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52062</v>
+        <v>52054</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0497</v>
+        <v>0.0496</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>51521</v>
+        <v>51501</v>
       </c>
       <c r="F88" t="n">
         <v>0.0491</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32060</v>
+        <v>32052</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:21</t>
+          <t>2026-08-02 11:17:14</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>14988</v>
+        <v>15017</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:21</t>
+          <t>2026-08-02 11:17:14</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:30</t>
+          <t>2026-08-02 11:18:10</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:21</t>
+          <t>2026-08-02 11:17:14</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:21</t>
+          <t>2026-08-02 11:17:14</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5808</v>
+        <v>5811</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:09</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:29</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="F190" t="n">
         <v>0.0013</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="F191" t="n">
         <v>0.0056</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5995</v>
+        <v>5997</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-08-01 11:18:28</t>
+          <t>2026-08-02 11:18:08</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>16847</v>
+        <v>16842</v>
       </c>
       <c r="F230" t="n">
         <v>0.0161</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:44</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>55932</v>
+        <v>55927</v>
       </c>
       <c r="F231" t="n">
         <v>0.0533</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:44</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:44</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>18940</v>
+        <v>18942</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:44</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>131352</v>
+        <v>131347</v>
       </c>
       <c r="F234" t="n">
         <v>0.1253</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:44</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>420691</v>
+        <v>420686</v>
       </c>
       <c r="F235" t="n">
         <v>0.4012</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>59976</v>
+        <v>59983</v>
       </c>
       <c r="F237" t="n">
         <v>0.0572</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7127</v>
+        <v>7126</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3292</v>
+        <v>3286</v>
       </c>
       <c r="F243" t="n">
         <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4577</v>
+        <v>4574</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5560</v>
+        <v>5554</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-08-01 11:17:45</t>
+          <t>2026-08-02 11:17:33</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17177</v>
+        <v>16007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0164</v>
+        <v>0.0153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:07</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81044</v>
+        <v>75992</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:07</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38299</v>
+        <v>36068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0365</v>
+        <v>0.0344</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:07</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19373</v>
+        <v>18382</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:07</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>172850</v>
+        <v>162643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1648</v>
+        <v>0.1551</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:07</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>467350</v>
+        <v>440859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4457</v>
+        <v>0.4204</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15836</v>
+        <v>15407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0151</v>
+        <v>0.0147</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55785</v>
+        <v>52992</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0532</v>
+        <v>0.0505</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7015</v>
+        <v>7016</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2148</v>
+        <v>2018</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8662</v>
+        <v>8166</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5321</v>
+        <v>5264</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6388</v>
+        <v>6314</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33796</v>
+        <v>32715</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0322</v>
+        <v>0.0312</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>161491</v>
+        <v>155520</v>
       </c>
       <c r="F19" t="n">
-        <v>0.154</v>
+        <v>0.1483</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71181</v>
+        <v>68888</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0679</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32957</v>
+        <v>31990</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0314</v>
+        <v>0.0305</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4768</v>
+        <v>4585</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18496</v>
+        <v>17881</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0176</v>
+        <v>0.0171</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6850</v>
+        <v>6771</v>
       </c>
       <c r="F24" t="n">
         <v>0.0065</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7797</v>
+        <v>7720</v>
       </c>
       <c r="F25" t="n">
         <v>0.0074</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:06</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1333,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>51335</v>
+        <v>51338</v>
       </c>
       <c r="F28" t="n">
         <v>0.049</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>51356</v>
+        <v>51359</v>
       </c>
       <c r="F53" t="n">
         <v>0.049</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>51322</v>
+        <v>52164</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0489</v>
+        <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51115</v>
+        <v>51909</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0487</v>
+        <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>52875</v>
+        <v>53750</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0504</v>
+        <v>0.0513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>52381</v>
+        <v>53222</v>
       </c>
       <c r="F71" t="n">
-        <v>0.05</v>
+        <v>0.0508</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>52214</v>
+        <v>53058</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0498</v>
+        <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2851,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52886</v>
+        <v>52892</v>
       </c>
       <c r="F74" t="n">
         <v>0.0504</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>51963</v>
+        <v>52817</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52078</v>
+        <v>52926</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0497</v>
+        <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52006</v>
+        <v>52859</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>52223</v>
+        <v>53063</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0498</v>
+        <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>52204</v>
+        <v>53047</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0498</v>
+        <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52054</v>
+        <v>52907</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0496</v>
+        <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>51501</v>
+        <v>52352</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0491</v>
+        <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3478,14 +3478,14 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10156</v>
+        <v>10157</v>
       </c>
       <c r="F93" t="n">
         <v>0.0097</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:14</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15017</v>
+        <v>15018</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:14</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8867</v>
+        <v>8888</v>
       </c>
       <c r="F97" t="n">
         <v>0.008500000000000001</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:10</t>
+          <t>2026-08-03 12:56:08</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10491</v>
+        <v>10131</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01</v>
+        <v>0.0097</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8071</v>
+        <v>8009</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:14</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:14</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5858</v>
+        <v>5859</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5662</v>
+        <v>5663</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4534,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="F125" t="n">
         <v>0.0056</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5811</v>
+        <v>5809</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:09</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5686</v>
+        <v>5687</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5854,14 +5854,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F165" t="n">
         <v>0.0056</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:55:24</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="F175" t="n">
         <v>0.0056</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5865</v>
+        <v>5867</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1124</v>
+        <v>1144</v>
       </c>
       <c r="F180" t="n">
         <v>0.0011</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5861</v>
+        <v>5883</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="F185" t="n">
         <v>0.0056</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1063</v>
+        <v>1081</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5815</v>
+        <v>5831</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6055</v>
+        <v>6056</v>
       </c>
       <c r="F189" t="n">
         <v>0.0058</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1319</v>
+        <v>1347</v>
       </c>
       <c r="F190" t="n">
         <v>0.0013</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5906</v>
+        <v>5925</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="F192" t="n">
         <v>0.0012</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5941</v>
+        <v>5959</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1245</v>
+        <v>1266</v>
       </c>
       <c r="F194" t="n">
         <v>0.0012</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5915</v>
+        <v>5933</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="F197" t="n">
         <v>0.0057</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5992</v>
+        <v>5991</v>
       </c>
       <c r="F199" t="n">
         <v>0.0057</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1219</v>
+        <v>1240</v>
       </c>
       <c r="F202" t="n">
         <v>0.0012</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5953</v>
+        <v>5972</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="F207" t="n">
         <v>0.0057</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1217</v>
+        <v>1236</v>
       </c>
       <c r="F208" t="n">
         <v>0.0012</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5997</v>
+        <v>6015</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F211" t="n">
         <v>0.0057</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1219</v>
+        <v>1239</v>
       </c>
       <c r="F212" t="n">
         <v>0.0012</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5990</v>
+        <v>6009</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1230</v>
+        <v>1251</v>
       </c>
       <c r="F214" t="n">
         <v>0.0012</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6007</v>
+        <v>6027</v>
       </c>
       <c r="F215" t="n">
         <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="F216" t="n">
         <v>0.0012</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6003</v>
+        <v>6023</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F219" t="n">
         <v>0.0057</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1216</v>
+        <v>1236</v>
       </c>
       <c r="F220" t="n">
         <v>0.0012</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5994</v>
+        <v>6014</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7834,14 +7834,14 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="F225" t="n">
         <v>0.0056</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1120</v>
+        <v>1139</v>
       </c>
       <c r="F226" t="n">
         <v>0.0011</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7900,14 +7900,14 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5820</v>
+        <v>5837</v>
       </c>
       <c r="F227" t="n">
         <v>0.0056</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="F229" t="n">
         <v>0.0057</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-08-02 11:18:08</t>
+          <t>2026-08-03 12:56:07</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>16842</v>
+        <v>16947</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0161</v>
+        <v>0.0162</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>55927</v>
+        <v>55984</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0533</v>
+        <v>0.0534</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>30889</v>
+        <v>30944</v>
       </c>
       <c r="F232" t="n">
         <v>0.0295</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>18942</v>
+        <v>18986</v>
       </c>
       <c r="F233" t="n">
         <v>0.0181</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>131347</v>
+        <v>132259</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1253</v>
+        <v>0.1261</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>420686</v>
+        <v>423663</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4012</v>
+        <v>0.404</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23329</v>
+        <v>23523</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0222</v>
+        <v>0.0224</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>59983</v>
+        <v>60278</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0572</v>
+        <v>0.0575</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="F241" t="n">
         <v>0.0068</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="F242" t="n">
         <v>0.0008</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3286</v>
+        <v>3292</v>
       </c>
       <c r="F243" t="n">
         <v>0.0031</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4574</v>
+        <v>4576</v>
       </c>
       <c r="F244" t="n">
         <v>0.0044</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8494,14 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5554</v>
+        <v>5556</v>
       </c>
       <c r="F245" t="n">
         <v>0.0053</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-08-02 11:17:33</t>
+          <t>2026-08-03 12:55:43</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16007</v>
+        <v>14948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0153</v>
+        <v>0.0143</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75992</v>
+        <v>71843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0725</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36068</v>
+        <v>33875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0344</v>
+        <v>0.0323</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18382</v>
+        <v>17473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0175</v>
+        <v>0.0167</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>162643</v>
+        <v>152435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1551</v>
+        <v>0.1454</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>440859</v>
+        <v>416025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4204</v>
+        <v>0.3968</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15407</v>
+        <v>14535</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0147</v>
+        <v>0.0139</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>52992</v>
+        <v>50361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0505</v>
+        <v>0.048</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2018</v>
+        <v>1888</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8166</v>
+        <v>7670</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.0073</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5264</v>
+        <v>5193</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6314</v>
+        <v>6230</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0059</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>32715</v>
+        <v>30481</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0312</v>
+        <v>0.0291</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>155520</v>
+        <v>149688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1483</v>
+        <v>0.1428</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68888</v>
+        <v>65436</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31990</v>
+        <v>30444</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0305</v>
+        <v>0.029</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4585</v>
+        <v>4291</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0044</v>
+        <v>0.0041</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17881</v>
+        <v>17127</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0171</v>
+        <v>0.0163</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6771</v>
+        <v>6724</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7720</v>
+        <v>7627</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:06</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51165</v>
+        <v>51986</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0488</v>
+        <v>0.0496</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51155</v>
+        <v>51975</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0488</v>
+        <v>0.0496</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1333,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>51338</v>
+        <v>52141</v>
       </c>
       <c r="F28" t="n">
-        <v>0.049</v>
+        <v>0.0497</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50141</v>
+        <v>50907</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0478</v>
+        <v>0.0485</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>50162</v>
+        <v>50928</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0478</v>
+        <v>0.0486</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>51407</v>
+        <v>52203</v>
       </c>
       <c r="F48" t="n">
-        <v>0.049</v>
+        <v>0.0498</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>51359</v>
+        <v>52162</v>
       </c>
       <c r="F53" t="n">
-        <v>0.049</v>
+        <v>0.0497</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>52099</v>
+        <v>52950</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0497</v>
+        <v>0.0505</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52068</v>
+        <v>52910</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0497</v>
+        <v>0.0505</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2323,14 +2323,14 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>51193</v>
+        <v>52048</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0488</v>
+        <v>0.0496</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52056</v>
+        <v>52058</v>
       </c>
       <c r="F63" t="n">
         <v>0.0496</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2521,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53645</v>
+        <v>54504</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0512</v>
+        <v>0.052</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2554,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>52164</v>
+        <v>52162</v>
       </c>
       <c r="F65" t="n">
         <v>0.0497</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>52176</v>
+        <v>52989</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0498</v>
+        <v>0.0505</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>51909</v>
+        <v>51923</v>
       </c>
       <c r="F68" t="n">
         <v>0.0495</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53750</v>
+        <v>53758</v>
       </c>
       <c r="F70" t="n">
         <v>0.0513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2752,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53222</v>
+        <v>53188</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53058</v>
+        <v>53067</v>
       </c>
       <c r="F72" t="n">
         <v>0.0506</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2884,14 +2884,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>51963</v>
+        <v>52800</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52817</v>
+        <v>52844</v>
       </c>
       <c r="F76" t="n">
         <v>0.0504</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52030</v>
+        <v>52862</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52926</v>
+        <v>52933</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52859</v>
+        <v>52849</v>
       </c>
       <c r="F81" t="n">
         <v>0.0504</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53063</v>
+        <v>53057</v>
       </c>
       <c r="F82" t="n">
         <v>0.0506</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53047</v>
+        <v>53048</v>
       </c>
       <c r="F83" t="n">
         <v>0.0506</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3214,14 +3214,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52907</v>
+        <v>52915</v>
       </c>
       <c r="F85" t="n">
         <v>0.0505</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3247,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>51995</v>
+        <v>52870</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0496</v>
+        <v>0.0504</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3313,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52352</v>
+        <v>52345</v>
       </c>
       <c r="F88" t="n">
         <v>0.0499</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3346,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53160</v>
+        <v>53970</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0507</v>
+        <v>0.0515</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -3511,14 +3511,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>32052</v>
+        <v>32055</v>
       </c>
       <c r="F94" t="n">
         <v>0.0306</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15018</v>
+        <v>15014</v>
       </c>
       <c r="F95" t="n">
         <v>0.0143</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8888</v>
+        <v>8874</v>
       </c>
       <c r="F97" t="n">
         <v>0.008500000000000001</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:08</t>
+          <t>2026-08-04 12:04:41</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10131</v>
+        <v>9515</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0097</v>
+        <v>0.0091</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3676,14 +3676,14 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>8009</v>
+        <v>7821</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -3775,14 +3775,14 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1088</v>
+        <v>1106</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5859</v>
+        <v>5875</v>
       </c>
       <c r="F103" t="n">
         <v>0.0056</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3841,14 +3841,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1090</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5866</v>
+        <v>5881</v>
       </c>
       <c r="F105" t="n">
         <v>0.0056</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3907,14 +3907,14 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="F106" t="n">
         <v>0.0012</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3940,14 +3940,14 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5803</v>
+        <v>5818</v>
       </c>
       <c r="F107" t="n">
         <v>0.0055</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -3973,14 +3973,14 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="F108" t="n">
         <v>0.0011</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4006,14 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5795</v>
+        <v>5808</v>
       </c>
       <c r="F109" t="n">
         <v>0.0055</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4072,14 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5727</v>
+        <v>5726</v>
       </c>
       <c r="F111" t="n">
         <v>0.0055</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4138,14 +4138,14 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5735</v>
+        <v>5734</v>
       </c>
       <c r="F113" t="n">
         <v>0.0055</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5727</v>
+        <v>5726</v>
       </c>
       <c r="F115" t="n">
         <v>0.0055</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4270,14 +4270,14 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5763</v>
+        <v>5762</v>
       </c>
       <c r="F117" t="n">
         <v>0.0055</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5663</v>
+        <v>5662</v>
       </c>
       <c r="F119" t="n">
         <v>0.0054</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4369,14 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="F120" t="n">
         <v>0.0011</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4402,14 +4402,14 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5795</v>
+        <v>5808</v>
       </c>
       <c r="F121" t="n">
         <v>0.0055</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4468,14 +4468,14 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="F123" t="n">
         <v>0.0057</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5807</v>
+        <v>5806</v>
       </c>
       <c r="F127" t="n">
         <v>0.0055</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5809</v>
+        <v>5808</v>
       </c>
       <c r="F129" t="n">
         <v>0.0055</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F131" t="n">
         <v>0.0055</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4798,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5750</v>
+        <v>5749</v>
       </c>
       <c r="F133" t="n">
         <v>0.0055</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4864,14 +4864,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5751</v>
+        <v>5750</v>
       </c>
       <c r="F135" t="n">
         <v>0.0055</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5776</v>
+        <v>5775</v>
       </c>
       <c r="F137" t="n">
         <v>0.0055</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5755</v>
+        <v>5754</v>
       </c>
       <c r="F139" t="n">
         <v>0.0055</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5766</v>
+        <v>5765</v>
       </c>
       <c r="F141" t="n">
         <v>0.0055</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5128,14 +5128,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5752</v>
+        <v>5751</v>
       </c>
       <c r="F143" t="n">
         <v>0.0055</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5194,14 +5194,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5801</v>
+        <v>5800</v>
       </c>
       <c r="F145" t="n">
         <v>0.0055</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5227,14 +5227,14 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1194</v>
+        <v>1214</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5260,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5865</v>
+        <v>5881</v>
       </c>
       <c r="F147" t="n">
         <v>0.0056</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5326,14 +5326,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5913</v>
+        <v>5912</v>
       </c>
       <c r="F149" t="n">
         <v>0.0056</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5458,14 +5458,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F153" t="n">
         <v>0.0056</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5687</v>
+        <v>5686</v>
       </c>
       <c r="F155" t="n">
         <v>0.0054</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5557,14 +5557,14 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="F156" t="n">
         <v>0.0012</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5803</v>
+        <v>5818</v>
       </c>
       <c r="F157" t="n">
         <v>0.0055</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5623,14 +5623,14 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1216</v>
+        <v>1237</v>
       </c>
       <c r="F158" t="n">
         <v>0.0012</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5656,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5952</v>
+        <v>5973</v>
       </c>
       <c r="F159" t="n">
         <v>0.0057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5689,14 +5689,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="F160" t="n">
         <v>0.0012</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5963</v>
+        <v>5981</v>
       </c>
       <c r="F161" t="n">
         <v>0.0057</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="F163" t="n">
         <v>0.0057</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -5887,14 +5887,14 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5920,14 +5920,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5939</v>
+        <v>5956</v>
       </c>
       <c r="F167" t="n">
         <v>0.0057</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F169" t="n">
         <v>0.0056</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:24</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -6118,14 +6118,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F173" t="n">
         <v>0.0056</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5867</v>
+        <v>5866</v>
       </c>
       <c r="F177" t="n">
         <v>0.0056</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1440</v>
+        <v>1464</v>
       </c>
       <c r="F178" t="n">
         <v>0.0014</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6048</v>
+        <v>6069</v>
       </c>
       <c r="F179" t="n">
         <v>0.0058</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="F181" t="n">
         <v>0.0056</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1213</v>
+        <v>1233</v>
       </c>
       <c r="F182" t="n">
         <v>0.0012</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5880</v>
+        <v>5897</v>
       </c>
       <c r="F183" t="n">
         <v>0.0056</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F186" t="n">
         <v>0.001</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F187" t="n">
         <v>0.0056</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="F191" t="n">
         <v>0.0057</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="F193" t="n">
         <v>0.0057</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1213</v>
+        <v>1233</v>
       </c>
       <c r="F200" t="n">
         <v>0.0012</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5977</v>
+        <v>5997</v>
       </c>
       <c r="F201" t="n">
         <v>0.0057</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F202" t="n">
         <v>0.0012</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5972</v>
+        <v>5974</v>
       </c>
       <c r="F203" t="n">
         <v>0.0057</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7141,14 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1217</v>
+        <v>1237</v>
       </c>
       <c r="F204" t="n">
         <v>0.0012</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5987</v>
+        <v>6005</v>
       </c>
       <c r="F205" t="n">
         <v>0.0057</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7306,14 +7306,14 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F209" t="n">
         <v>0.0057</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:02:52</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7438,14 +7438,14 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="F213" t="n">
         <v>0.0057</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="F215" t="n">
         <v>0.0057</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F217" t="n">
         <v>0.0057</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="F221" t="n">
         <v>0.0057</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1211</v>
+        <v>1231</v>
       </c>
       <c r="F222" t="n">
         <v>0.0012</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5981</v>
+        <v>5998</v>
       </c>
       <c r="F223" t="n">
         <v>0.0057</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:40</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1363</v>
+        <v>1381</v>
       </c>
       <c r="F228" t="n">
         <v>0.0013</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7966,14 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6014</v>
+        <v>6032</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-08-03 12:56:07</t>
+          <t>2026-08-04 12:04:39</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>16947</v>
+        <v>15788</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0162</v>
+        <v>0.0151</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:43</t>
+          <t>2026-08-04 12:03:11</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>55984</v>
+        <v>55277</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0534</v>
+        <v>0.0527</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:43</t>
+          <t>2026-08-04 12:03:11</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>30944</v>
+        <v>29826</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0295</v>
+        <v>0.0284</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:43</t>
+          <t>2026-08-04 12:03:11</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>18986</v>
+        <v>18423</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0181</v>
+        <v>0.0176</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-08-03 12:55:43</t>
+          <t>2026-08-04 12:03:11</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>132259</v>
+        <v>123510</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1261</v>
+        <v>0.1178</v>
     